--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -30008,7 +30008,7 @@
           <t>C | 589呎 (2房)
 $2,019万
 $34,273/呎
-(26年-01月)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -31536,7 +31536,7 @@
           <t>A | 955呎 (3房)
 $3,711万
 $38,854/呎
-(25年-09月)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -32416,7 +32416,7 @@
           <t>A | 955呎 (3房)
 $3,267万
 $34,212/呎
-(25年-03月)</t>
+(已售)</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -32613,7 +32613,7 @@
           <t>E | 341呎 (1房)
 $1,070万
 $31,385/呎
-(26年-03月)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -25016,7 +25016,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -32894,11 +32894,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -32906,7 +32927,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -32914,8 +32935,8 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -32923,7 +32944,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -32931,7 +32952,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -32940,27 +32961,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
           <t>G | 470呎 (2房)
 $1343万
 $28,565/呎
-(24年-04月)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -32894,10 +32894,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -32905,61 +32954,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -212,61 +212,61 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -32894,11 +32894,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -32906,7 +32927,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -32914,8 +32935,8 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -32923,7 +32944,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -32931,7 +32952,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -32939,27 +32960,6 @@
 (22年-05月)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -212,61 +212,61 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -32894,10 +32894,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -32905,61 +32954,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>19590500</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>33317</v>
+        <v>33261</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -30597,9 +30597,9 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 588呎 (2房)
+          <t>C | 589呎 (2房)
 $1959万
-$33,317/呎
+$33,261/呎
 (21年-10月)</t>
         </is>
       </c>
@@ -32894,11 +32894,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -32906,7 +32927,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -32914,8 +32935,8 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -32923,7 +32944,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -32931,7 +32952,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -32939,27 +32960,6 @@
 (22年-05月)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -38131,7 +38131,7 @@
           <t>A | 1848呎 (4+房)
 $13900万
 $75,216/呎
-(22年-02月-20日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -38139,7 +38139,7 @@
           <t>B | 1102呎 (3房)
 $4972万
 $45,120/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -38165,7 +38165,7 @@
           <t>B | 934呎 (3房)
 $4522万
 $48,415/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -38173,7 +38173,7 @@
           <t>C | 524呎 (2房)
 $1872万
 $35,730/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -38181,7 +38181,7 @@
           <t>D | 751呎 (3房)
 $2360万
 $31,431/呎
-(23年-12月-26日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -38189,7 +38189,7 @@
           <t>E | 496呎 (2房)
 $1800万
 $36,293/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -38212,7 +38212,7 @@
           <t>B | 934呎 (3房)
 $4477万
 $47,936/呎
-(22年-02月-09日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -38220,7 +38220,7 @@
           <t>C | 524呎 (2房)
 $1867万
 $35,623/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -38228,7 +38228,7 @@
           <t>D | 751呎 (3房)
 $2769万
 $36,867/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -38236,7 +38236,7 @@
           <t>E | 496呎 (2房)
 $1795万
 $36,184/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38251,7 +38251,7 @@
           <t>A | 1299呎 (4+房)
 $7469万
 $57,500/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -38259,7 +38259,7 @@
           <t>B | 934呎 (3房)
 $4167万
 $44,615/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -38267,7 +38267,7 @@
           <t>C | 524呎 (2房)
 $1861万
 $35,518/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -38275,7 +38275,7 @@
           <t>D | 751呎 (3房)
 $2312万
 $30,784/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -38283,7 +38283,7 @@
           <t>E | 496呎 (2房)
 $1789万
 $36,076/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
           <t>A | 1299呎 (4+房)
 $6300万
 $48,499/呎
-(23年-04月-20日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -38306,7 +38306,7 @@
           <t>B | 934呎 (3房)
 $4360万
 $46,681/呎
-(23年-04月-25日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -38314,7 +38314,7 @@
           <t>C | 524呎 (2房)
 $1925万
 $36,740/呎
-(21年-11月-10日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -38322,7 +38322,7 @@
           <t>D | 751呎 (3房)
 $2760万
 $36,758/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -38330,7 +38330,7 @@
           <t>E | 496呎 (2房)
 $1511万
 $30,465/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38345,7 +38345,7 @@
           <t>A | 1299呎 (4+房)
 $6174万
 $47,530/呎
-(24年-01月-11日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -38353,7 +38353,7 @@
           <t>B | 934呎 (3房)
 $4282万
 $45,843/呎
-(23年-02月-21日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -38361,7 +38361,7 @@
           <t>C | 524呎 (2房)
 $1866万
 $35,605/呎
-(23年-05月-08日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -38369,7 +38369,7 @@
           <t>D | 751呎 (3房)
 $2613万
 $34,798/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>E | 496呎 (2房)
 $1669万
 $33,647/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -38392,7 +38392,7 @@
           <t>A | 1299呎 (4+房)
 $6240万
 $48,037/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -38400,7 +38400,7 @@
           <t>B | 934呎 (3房)
 $4278万
 $45,798/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -38408,7 +38408,7 @@
           <t>C | 524呎 (2房)
 $1817万
 $34,678/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -38416,7 +38416,7 @@
           <t>D | 751呎 (3房)
 $2736万
 $36,429/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -38424,7 +38424,7 @@
           <t>E | 496呎 (2房)
 $1664万
 $33,547/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38439,7 +38439,7 @@
           <t>A | 1299呎 (4+房)
 $6180万
 $47,575/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -38447,7 +38447,7 @@
           <t>B | 934呎 (3房)
 $4235万
 $45,345/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -38455,7 +38455,7 @@
           <t>C | 524呎 (2房)
 $1812万
 $34,573/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -38463,7 +38463,7 @@
           <t>D | 751呎 (3房)
 $2728万
 $36,320/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -38471,7 +38471,7 @@
           <t>E | 496呎 (2房)
 $1659万
 $33,445/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -38486,7 +38486,7 @@
           <t>A | 1299呎 (4+房)
 $6138万
 $47,252/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -38494,7 +38494,7 @@
           <t>B | 934呎 (3房)
 $4193万
 $44,896/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -38502,7 +38502,7 @@
           <t>C | 524呎 (2房)
 $1806万
 $34,470/呎
-(23年-05月-24日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -38510,7 +38510,7 @@
           <t>D | 751呎 (3房)
 $2331万
 $31,039/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -38518,7 +38518,7 @@
           <t>E | 496呎 (2房)
 $1694万
 $34,159/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
           <t>A | 1299呎 (4+房)
 $5716万
 $44,004/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -38541,7 +38541,7 @@
           <t>B | 934呎 (3房)
 $3954万
 $42,334/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -38549,7 +38549,7 @@
           <t>C | 524呎 (2房)
 $1508万
 $28,783/呎
-(24年-02月-19日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -38557,7 +38557,7 @@
           <t>D | 751呎 (3房)
 $2711万
 $36,103/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -38565,7 +38565,7 @@
           <t>E | 496呎 (2房)
 $1689万
 $34,057/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38580,7 +38580,7 @@
           <t>A | 1299呎 (4+房)
 $5328万
 $41,016/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -38588,7 +38588,7 @@
           <t>B | 934呎 (3房)
 $4016万
 $43,000/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -38596,7 +38596,7 @@
           <t>C | 524呎 (2房)
 $1885万
 $35,979/呎
-(21年-10月-19日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -38604,7 +38604,7 @@
           <t>D | 751呎 (3房)
 $2655万
 $35,353/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -38612,7 +38612,7 @@
           <t>E | 496呎 (2房)
 $1604万
 $32,339/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38627,7 +38627,7 @@
           <t>A | 1299呎 (4+房)
 $5680万
 $43,726/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -38635,7 +38635,7 @@
           <t>B | 934呎 (3房)
 $3960万
 $42,402/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -38643,7 +38643,7 @@
           <t>C | 524呎 (2房)
 $1880万
 $35,872/呎
-(21年-09月-17日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -38651,7 +38651,7 @@
           <t>D | 751呎 (3房)
 $2695万
 $35,886/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -38659,7 +38659,7 @@
           <t>E | 497呎 (2房)
 $1639万
 $32,981/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38674,7 +38674,7 @@
           <t>A | 1299呎 (4+房)
 $5389万
 $41,485/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -38682,7 +38682,7 @@
           <t>B | 934呎 (3房)
 $3933万
 $42,107/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -38690,7 +38690,7 @@
           <t>C | 524呎 (2房)
 $1495万
 $28,526/呎
-(23年-12月-28日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -38698,7 +38698,7 @@
           <t>D | 751呎 (3房)
 $2559万
 $34,076/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -38706,7 +38706,7 @@
           <t>E | 497呎 (2房)
 $1594万
 $32,080/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38721,7 +38721,7 @@
           <t>A | 1299呎 (4+房)
 $5849万
 $45,030/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -38729,7 +38729,7 @@
           <t>B | 934呎 (3房)
 $4206万
 $45,029/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -38737,7 +38737,7 @@
           <t>C | 524呎 (2房)
 $1495万
 $28,526/呎
-(23年-11月-24日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -38745,7 +38745,7 @@
           <t>D | 751呎 (3房)
 $2559万
 $34,076/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -38753,7 +38753,7 @@
           <t>E | 497呎 (2房)
 $1674万
 $33,685/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38768,7 +38768,7 @@
           <t>A | 1299呎 (4+房)
 $5164万
 $39,758/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -38776,7 +38776,7 @@
           <t>B | 934呎 (3房)
 $3951万
 $42,301/呎
-(23年-02月-19日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -38784,7 +38784,7 @@
           <t>C | 524呎 (2房)
 $1774万
 $33,858/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -38792,7 +38792,7 @@
           <t>D | 751呎 (3房)
 $2544万
 $33,874/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -38800,7 +38800,7 @@
           <t>E | 497呎 (2房)
 $1426万
 $28,700/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38815,7 +38815,7 @@
           <t>A | 1299呎 (4+房)
 $4880万
 $37,567/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -38823,7 +38823,7 @@
           <t>B | 934呎 (3房)
 $3688万
 $39,481/呎
-(23年-12月-14日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -38831,7 +38831,7 @@
           <t>C | 524呎 (2房)
 $1481万
 $28,272/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -38839,7 +38839,7 @@
           <t>D | 751呎 (3房)
 $2663万
 $35,459/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -38847,7 +38847,7 @@
           <t>E | 497呎 (2房)
 $1580万
 $31,792/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38862,7 +38862,7 @@
           <t>A | 1299呎 (4+房)
 $5040万
 $38,800/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -38870,7 +38870,7 @@
           <t>B | 934呎 (3房)
 $3974万
 $42,549/呎
-(21年-09月-17日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -38878,7 +38878,7 @@
           <t>C | 524呎 (2房)
 $1499万
 $28,609/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -38886,7 +38886,7 @@
           <t>D | 751呎 (3房)
 $2529万
 $33,669/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -38894,7 +38894,7 @@
           <t>E | 497呎 (2房)
 $1654万
 $33,286/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38909,7 +38909,7 @@
           <t>A | 1299呎 (4+房)
 $5238万
 $40,320/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -38917,7 +38917,7 @@
           <t>B | 934呎 (3房)
 $3766万
 $40,322/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -38925,7 +38925,7 @@
           <t>C | 524呎 (2房)
 $1473万
 $28,104/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -38933,7 +38933,7 @@
           <t>D | 751呎 (3房)
 $2521万
 $33,569/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -38941,7 +38941,7 @@
           <t>E | 497呎 (2房)
 $1620万
 $32,593/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -38956,7 +38956,7 @@
           <t>A | 1299呎 (4+房)
 $5472万
 $42,125/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -38964,7 +38964,7 @@
           <t>B | 934呎 (3房)
 $3747万
 $40,121/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -38972,7 +38972,7 @@
           <t>C | 524呎 (2房)
 $1468万
 $28,020/呎
-(23年-12月-27日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -38980,7 +38980,7 @@
           <t>D | 751呎 (3房)
 $2514万
 $33,469/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -38988,7 +38988,7 @@
           <t>E | 497呎 (2房)
 $1605万
 $32,299/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39003,7 +39003,7 @@
           <t>A | 1299呎 (4+房)
 $4875万
 $37,529/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -39011,7 +39011,7 @@
           <t>B | 934呎 (3房)
 $3505万
 $37,526/呎
-(24年-08月-12日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39019,7 +39019,7 @@
           <t>C | 524呎 (2房)
 $1464万
 $27,937/呎
-(24年-03月-12日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -39027,7 +39027,7 @@
           <t>D | 751呎 (3房)
 $2506万
 $33,369/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -39035,7 +39035,7 @@
           <t>E | 497呎 (2房)
 $1561万
 $31,417/呎
-(21年-09月-19日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39050,7 +39050,7 @@
           <t>A | 1299呎 (4+房)
 $5365万
 $41,298/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -39058,7 +39058,7 @@
           <t>B | 934呎 (3房)
 $3674万
 $39,331/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39066,7 +39066,7 @@
           <t>C | 524呎 (2房)
 $1417万
 $27,044/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -39074,7 +39074,7 @@
           <t>D | 751呎 (3房)
 $2623万
 $34,931/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -39082,7 +39082,7 @@
           <t>E | 497呎 (2房)
 $1635万
 $32,889/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39097,7 +39097,7 @@
           <t>A | 1299呎 (4+房)
 $4704万
 $36,216/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -39105,7 +39105,7 @@
           <t>B | 934呎 (3房)
 $3819万
 $40,888/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39113,7 +39113,7 @@
           <t>C | 524呎 (2房)
 $1409万
 $26,885/呎
-(24年-03月-07日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -39121,7 +39121,7 @@
           <t>D | 751呎 (3房)
 $2608万
 $34,723/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -39129,7 +39129,7 @@
           <t>E | 497呎 (2房)
 $1625万
 $32,693/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
           <t>A | 1299呎 (4+房)
 $4731万
 $36,423/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -39152,7 +39152,7 @@
           <t>B | 934呎 (3房)
 $3800万
 $40,685/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39160,7 +39160,7 @@
           <t>C | 524呎 (2房)
 $1405万
 $26,804/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -39168,7 +39168,7 @@
           <t>D | 751呎 (3房)
 $2476万
 $32,970/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -39176,7 +39176,7 @@
           <t>E | 497呎 (2房)
 $1620万
 $32,596/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39191,7 +39191,7 @@
           <t>A | 1229呎 (4+房)
 $5430万
 $44,181/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -39199,7 +39199,7 @@
           <t>B | 874呎 (3房)
 $3861万
 $44,180/呎
-(23年-12月-21日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39207,7 +39207,7 @@
           <t>C | 487呎 (2房)
 $1694万
 $34,778/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -39215,7 +39215,7 @@
           <t>D | 709呎 (3房)
 $2482万
 $35,000/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -39223,7 +39223,7 @@
           <t>E | 461呎 (2房)
 $1567万
 $34,001/呎
-(22年-02月-13日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -39373,7 +39373,7 @@
           <t>A | 1902呎 (4+房)
 $13000万
 $68,349/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -39389,7 +39389,7 @@
           <t>C | 1000呎 (3房)
 $4700万
 $47,000/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -39407,7 +39407,7 @@
           <t>A | 1420呎 (4+房)
 $8557万
 $60,260/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -39415,7 +39415,7 @@
           <t>B | 942呎 (3房)
 $4553万
 $48,334/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -39423,7 +39423,7 @@
           <t>C | 589呎 (2房)
 $1981万
 $33,630/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -39431,7 +39431,7 @@
           <t>D | 481呎 (2房)
 $1602万
 $33,314/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -39439,7 +39439,7 @@
           <t>E | 523呎 (2房)
 $1817万
 $34,733/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -39447,7 +39447,7 @@
           <t>F | 464呎 (2房)
 $1386万
 $29,861/呎
-(24年-01月-13日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -39470,7 +39470,7 @@
           <t>B | 942呎 (3房)
 $4095万
 $43,471/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -39478,7 +39478,7 @@
           <t>C | 589呎 (2房)
 $1975万
 $33,529/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -39486,7 +39486,7 @@
           <t>D | 481呎 (2房)
 $1678万
 $34,877/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -39494,7 +39494,7 @@
           <t>E | 523呎 (2房)
 $1806万
 $34,527/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -39502,7 +39502,7 @@
           <t>F | 464呎 (2房)
 $1698万
 $36,586/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -39517,7 +39517,7 @@
           <t>A | 1420呎 (4+房)
 $8520万
 $60,000/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -39525,7 +39525,7 @@
           <t>B | 941呎 (3房)
 $4360万
 $46,332/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -39533,7 +39533,7 @@
           <t>C | 589呎 (2房)
 $1969万
 $33,429/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -39541,7 +39541,7 @@
           <t>D | 481呎 (2房)
 $1673万
 $34,772/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -39549,7 +39549,7 @@
           <t>E | 524呎 (2房)
 $1887万
 $36,005/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -39557,7 +39557,7 @@
           <t>F | 464呎 (2房)
 $1638万
 $35,302/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -39572,7 +39572,7 @@
           <t>A | 1420呎 (4+房)
 $7025万
 $49,470/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -39580,7 +39580,7 @@
           <t>B | 942呎 (3房)
 $3651万
 $38,759/呎
-(25年-02月-11日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39588,7 +39588,7 @@
           <t>C | 589呎 (2房)
 $1940万
 $32,934/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -39596,7 +39596,7 @@
           <t>D | 481呎 (2房)
 $1600万
 $33,270/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -39604,7 +39604,7 @@
           <t>E | 524呎 (2房)
 $1703万
 $32,498/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -39612,7 +39612,7 @@
           <t>F | 464呎 (2房)
 $1614万
 $34,779/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -39627,7 +39627,7 @@
           <t>A | 1420呎 (4+房)
 $6887万
 $48,500/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -39635,7 +39635,7 @@
           <t>B | 942呎 (3房)
 $4085万
 $43,364/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39643,7 +39643,7 @@
           <t>C | 589呎 (2房)
 $2025万
 $34,376/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -39651,7 +39651,7 @@
           <t>D | 481呎 (2房)
 $1591万
 $33,069/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -39659,7 +39659,7 @@
           <t>E | 524呎 (2房)
 $1686万
 $32,174/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -39667,7 +39667,7 @@
           <t>F | 464呎 (2房)
 $1598万
 $34,434/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -39682,7 +39682,7 @@
           <t>A | 1420呎 (4+房)
 $6929万
 $48,796/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -39690,7 +39690,7 @@
           <t>B | 941呎 (3房)
 $4168万
 $44,288/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -39698,7 +39698,7 @@
           <t>C | 589呎 (2房)
 $2019万
 $34,273/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -39706,7 +39706,7 @@
           <t>D | 481呎 (2房)
 $1510万
 $31,400/呎
-(21年-09月-19日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -39714,7 +39714,7 @@
           <t>E | 524呎 (2房)
 $1678万
 $32,014/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -39722,7 +39722,7 @@
           <t>F | 464呎 (2房)
 $1640万
 $35,335/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39737,7 +39737,7 @@
           <t>A | 1420呎 (4+房)
 $6958万
 $48,997/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>B | 941呎 (3房)
 $3930万
 $41,762/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>C | 589呎 (2房)
 $2013万
 $34,170/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -39761,7 +39761,7 @@
           <t>D | 481呎 (2房)
 $1544万
 $32,091/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -39769,7 +39769,7 @@
           <t>E | 524呎 (2房)
 $1735万
 $33,119/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -39777,7 +39777,7 @@
           <t>F | 464呎 (2房)
 $1566万
 $33,759/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -39792,7 +39792,7 @@
           <t>A | 1420呎 (4+房)
 $7009万
 $49,358/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -39800,7 +39800,7 @@
           <t>B | 942呎 (3房)
 $4085万
 $43,370/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39808,7 +39808,7 @@
           <t>C | 589呎 (2房)
 $1971万
 $33,459/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -39816,7 +39816,7 @@
           <t>D | 481呎 (2房)
 $1561万
 $32,449/呎
-(21年-09月-19日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>E | 523呎 (2房)
 $1710万
 $32,689/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -39832,7 +39832,7 @@
           <t>F | 464呎 (2房)
 $1559万
 $33,591/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -39847,7 +39847,7 @@
           <t>A | 1420呎 (4+房)
 $6532万
 $46,002/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -39855,7 +39855,7 @@
           <t>B | 941呎 (3房)
 $3852万
 $40,938/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39863,7 +39863,7 @@
           <t>C | 589呎 (2房)
 $1905万
 $32,346/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -39871,7 +39871,7 @@
           <t>D | 481呎 (2房)
 $1334万
 $27,731/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -39879,7 +39879,7 @@
           <t>E | 524呎 (2房)
 $1620万
 $30,918/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -39887,7 +39887,7 @@
           <t>F | 464呎 (2房)
 $1299万
 $27,993/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -39902,7 +39902,7 @@
           <t>A | 1420呎 (4+房)
 $6816万
 $48,000/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -39910,7 +39910,7 @@
           <t>B | 942呎 (3房)
 $3905万
 $41,456/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -39918,7 +39918,7 @@
           <t>C | 589呎 (2房)
 $1900万
 $32,250/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -39926,7 +39926,7 @@
           <t>D | 481呎 (2房)
 $1524万
 $31,679/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -39934,7 +39934,7 @@
           <t>E | 523呎 (2房)
 $1646万
 $31,475/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -39942,7 +39942,7 @@
           <t>F | 464呎 (2房)
 $1528万
 $32,931/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -39957,7 +39957,7 @@
           <t>A | 1420呎 (4+房)
 $6404万
 $45,100/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -39965,7 +39965,7 @@
           <t>B | 942呎 (3房)
 $3695万
 $39,223/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39973,7 +39973,7 @@
           <t>C | 588呎 (2房)
 $1894万
 $32,211/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -39981,7 +39981,7 @@
           <t>D | 481呎 (2房)
 $1547万
 $32,159/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -39989,7 +39989,7 @@
           <t>E | 523呎 (2房)
 $1668万
 $31,888/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -39997,7 +39997,7 @@
           <t>F | 464呎 (2房)
 $1520万
 $32,766/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40012,7 +40012,7 @@
           <t>A | 1420呎 (4+房)
 $6107万
 $43,010/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -40020,7 +40020,7 @@
           <t>B | 942呎 (3房)
 $3784万
 $40,167/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -40028,7 +40028,7 @@
           <t>C | 588呎 (2房)
 $1888万
 $32,114/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -40036,7 +40036,7 @@
           <t>D | 481呎 (2房)
 $1542万
 $32,063/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -40044,7 +40044,7 @@
           <t>E | 523呎 (2房)
 $1422万
 $27,196/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -40052,7 +40052,7 @@
           <t>F | 464呎 (2房)
 $1560万
 $33,621/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40067,7 +40067,7 @@
           <t>A | 1420呎 (4+房)
 $5900万
 $41,549/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -40075,7 +40075,7 @@
           <t>B | 942呎 (3房)
 $3660万
 $38,854/呎
-(23年-11月-28日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -40083,7 +40083,7 @@
           <t>C | 589呎 (2房)
 $1888万
 $32,060/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -40091,7 +40091,7 @@
           <t>D | 481呎 (2房)
 $1469万
 $30,536/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -40099,7 +40099,7 @@
           <t>E | 523呎 (2房)
 $1580万
 $30,218/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -40107,7 +40107,7 @@
           <t>F | 464呎 (2房)
 $1513万
 $32,602/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
           <t>A | 1420呎 (4+房)
 $6292万
 $44,308/呎
-(22年-06月-20日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -40130,7 +40130,7 @@
           <t>B | 942呎 (3房)
 $3652万
 $38,770/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40138,7 +40138,7 @@
           <t>C | 588呎 (2房)
 $1971万
 $33,517/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -40146,7 +40146,7 @@
           <t>D | 481呎 (2房)
 $1460万
 $30,355/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -40154,7 +40154,7 @@
           <t>E | 523呎 (2房)
 $1565万
 $29,920/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -40162,7 +40162,7 @@
           <t>F | 464呎 (2房)
 $1535万
 $33,088/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -40177,7 +40177,7 @@
           <t>A | 1420呎 (4+房)
 $5623万
 $39,600/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -40185,7 +40185,7 @@
           <t>B | 942呎 (3房)
 $3627万
 $38,499/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40193,7 +40193,7 @@
           <t>C | 588呎 (2房)
 $1965万
 $33,416/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -40201,7 +40201,7 @@
           <t>D | 481呎 (2房)
 $1528万
 $31,777/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -40209,7 +40209,7 @@
           <t>E | 523呎 (2房)
 $1638万
 $31,321/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -40217,7 +40217,7 @@
           <t>F | 465呎 (2房)
 $1568万
 $33,719/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40232,7 +40232,7 @@
           <t>A | 1420呎 (4+房)
 $6262万
 $44,101/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -40240,7 +40240,7 @@
           <t>B | 942呎 (3房)
 $3887万
 $41,258/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -40248,7 +40248,7 @@
           <t>C | 589呎 (2房)
 $1959万
 $33,261/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -40256,7 +40256,7 @@
           <t>D | 481呎 (2房)
 $1524万
 $31,684/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -40264,7 +40264,7 @@
           <t>E | 523呎 (2房)
 $1604万
 $30,670/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -40272,7 +40272,7 @@
           <t>F | 465呎 (2房)
 $1563万
 $33,618/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40287,7 +40287,7 @@
           <t>A | 1420呎 (4+房)
 $6231万
 $43,881/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -40295,7 +40295,7 @@
           <t>B | 942呎 (3房)
 $3867万
 $41,053/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40303,7 +40303,7 @@
           <t>C | 588呎 (2房)
 $1860万
 $31,635/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -40311,7 +40311,7 @@
           <t>D | 481呎 (2房)
 $1447万
 $30,084/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -40319,7 +40319,7 @@
           <t>E | 523呎 (2房)
 $1628万
 $31,133/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -40327,7 +40327,7 @@
           <t>F | 464呎 (2房)
 $1559万
 $33,591/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40342,7 +40342,7 @@
           <t>A | 1420呎 (4+房)
 $5905万
 $41,584/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -40350,7 +40350,7 @@
           <t>B | 942呎 (3房)
 $3555万
 $37,738/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40358,7 +40358,7 @@
           <t>C | 588呎 (2房)
 $1855万
 $31,541/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -40366,7 +40366,7 @@
           <t>D | 481呎 (2房)
 $1443万
 $29,993/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -40374,7 +40374,7 @@
           <t>E | 523呎 (2房)
 $1546万
 $29,562/呎
-(21年-09月-22日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -40382,7 +40382,7 @@
           <t>F | 465呎 (2房)
 $1239万
 $26,653/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -40397,7 +40397,7 @@
           <t>A | 1420呎 (4+房)
 $5910万
 $41,618/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -40405,7 +40405,7 @@
           <t>B | 941呎 (3房)
 $3829万
 $40,689/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -40413,7 +40413,7 @@
           <t>C | 589呎 (2房)
 $1907万
 $32,375/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -40421,7 +40421,7 @@
           <t>D | 481呎 (2房)
 $1510万
 $31,398/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -40429,7 +40429,7 @@
           <t>E | 523呎 (2房)
 $1590万
 $30,396/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -40437,7 +40437,7 @@
           <t>F | 465呎 (2房)
 $1549万
 $33,315/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40452,7 +40452,7 @@
           <t>A | 1420呎 (4+房)
 $5214万
 $36,721/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -40460,7 +40460,7 @@
           <t>B | 942呎 (3房)
 $3732万
 $39,616/呎
-(21年-09月-17日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -40468,7 +40468,7 @@
           <t>C | 588呎 (2房)
 $1844万
 $31,354/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -40476,7 +40476,7 @@
           <t>D | 481呎 (2房)
 $1434万
 $29,813/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -40484,7 +40484,7 @@
           <t>E | 523呎 (2房)
 $1537万
 $29,386/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -40492,7 +40492,7 @@
           <t>F | 465呎 (2房)
 $1471万
 $31,635/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40515,7 +40515,7 @@
           <t>B | 941呎 (3房)
 $3519万
 $37,396/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -40523,7 +40523,7 @@
           <t>C | 588呎 (2房)
 $1924万
 $32,724/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -40531,7 +40531,7 @@
           <t>D | 481呎 (2房)
 $1497万
 $31,119/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -40539,7 +40539,7 @@
           <t>E | 523呎 (2房)
 $1394万
 $26,657/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -40547,7 +40547,7 @@
           <t>F | 464呎 (2房)
 $1535万
 $33,091/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40570,7 +40570,7 @@
           <t>B | 942呎 (3房)
 $3677万
 $39,029/呎
-(21年-10月-14日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40578,7 +40578,7 @@
           <t>C | 588呎 (2房)
 $1918万
 $32,627/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -40586,7 +40586,7 @@
           <t>D | 481呎 (2房)
 $1492万
 $31,024/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -40594,7 +40594,7 @@
           <t>E | 523呎 (2房)
 $1599万
 $30,580/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -40602,7 +40602,7 @@
           <t>F | 465呎 (2房)
 $1531万
 $32,921/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -40617,7 +40617,7 @@
           <t>A | 1352呎 (4+房)
 $5556万
 $41,091/呎
-(25年-05月-25日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -40625,7 +40625,7 @@
           <t>B | 882呎 (3房)
 $3902万
 $44,240/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40633,7 +40633,7 @@
           <t>C | 549呎 (2房)
 $1867万
 $34,001/呎
-(22年-02月-15日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -40641,7 +40641,7 @@
           <t>D | 443呎 (2房)
 $1462万
 $33,000/呎
-(22年-02月-15日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -40649,7 +40649,7 @@
           <t>E | 485呎 (2房)
 $1600万
 $33,000/呎
-(22年-02月-16日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -40657,7 +40657,7 @@
           <t>F | 425呎 (2房)
 $1424万
 $33,500/呎
-(22年-02月-15日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -40841,7 +40841,7 @@
           <t>A | 955呎 (3房)
 $4102万
 $42,955/呎
-(22年-02月-16日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -40849,7 +40849,7 @@
           <t>B | 842呎 (3房)
 $3245万
 $38,536/呎
-(22年-03月-09日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -40857,7 +40857,7 @@
           <t>C | 850呎 (3房)
 $3476万
 $40,892/呎
-(23年-02月-26日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -40865,7 +40865,7 @@
           <t>D | 920呎 (3房)
 $3630万
 $39,454/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -40873,7 +40873,7 @@
           <t>E | 341呎 (1房)
 $1257万
 $36,874/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -40881,7 +40881,7 @@
           <t>F | 604呎 (2房)
 $1782万
 $29,499/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -40896,7 +40896,7 @@
           <t>A | 955呎 (3房)
 $3249万
 $34,024/呎
-(23年-12月-21日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -40904,7 +40904,7 @@
           <t>B | 842呎 (3房)
 $3222万
 $38,268/呎
-(23年-03月-07日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -40912,7 +40912,7 @@
           <t>C | 850呎 (3房)
 $3452万
 $40,608/呎
-(23年-02月-26日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -40920,7 +40920,7 @@
           <t>D | 920呎 (3房)
 $3605万
 $39,180/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -40928,7 +40928,7 @@
           <t>E | 341呎 (1房)
 $1194万
 $35,012/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -40936,7 +40936,7 @@
           <t>F | 604呎 (2房)
 $1776万
 $29,409/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -40951,7 +40951,7 @@
           <t>A | 955呎 (3房)
 $3227万
 $33,788/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -40959,7 +40959,7 @@
           <t>B | 842呎 (3房)
 $3200万
 $38,002/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -40967,7 +40967,7 @@
           <t>C | 850呎 (3房)
 $2871万
 $33,772/呎
-(23年-12月-28日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -40975,7 +40975,7 @@
           <t>D | 920呎 (3房)
 $3580万
 $38,908/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -40983,7 +40983,7 @@
           <t>E | 341呎 (1房)
 $1190万
 $34,904/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -40991,7 +40991,7 @@
           <t>F | 604呎 (2房)
 $1771万
 $29,323/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41006,7 +41006,7 @@
           <t>A | 955呎 (3房)
 $3634万
 $38,051/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -41014,7 +41014,7 @@
           <t>B | 842呎 (3房)
 $3289万
 $39,056/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -41022,7 +41022,7 @@
           <t>C | 850呎 (3房)
 $3233万
 $38,031/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -41030,7 +41030,7 @@
           <t>D | 921呎 (3房)
 $3487万
 $37,861/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -41038,7 +41038,7 @@
           <t>E | 341呎 (1房)
 $1246万
 $36,544/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -41046,7 +41046,7 @@
           <t>F | 604呎 (2房)
 $1766万
 $29,234/呎
-(24年-07月-04日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -41061,7 +41061,7 @@
           <t>A | 955呎 (3房)
 $3609万
 $37,786/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -41069,7 +41069,7 @@
           <t>B | 842呎 (3房)
 $3110万
 $36,938/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -41077,7 +41077,7 @@
           <t>C | 850呎 (3房)
 $3210万
 $37,767/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -41085,7 +41085,7 @@
           <t>D | 921呎 (3房)
 $3298万
 $35,807/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -41093,7 +41093,7 @@
           <t>E | 341呎 (1房)
 $1183万
 $34,698/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -41101,7 +41101,7 @@
           <t>F | 604呎 (2房)
 $1760万
 $29,147/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41116,7 +41116,7 @@
           <t>A | 955呎 (3房)
 $3584万
 $37,524/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -41124,7 +41124,7 @@
           <t>B | 842呎 (3房)
 $3185万
 $37,827/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -41132,7 +41132,7 @@
           <t>C | 850呎 (3房)
 $3188万
 $37,504/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -41140,7 +41140,7 @@
           <t>D | 921呎 (3房)
 $3439万
 $37,337/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -41148,7 +41148,7 @@
           <t>E | 341呎 (1房)
 $1180万
 $34,597/呎
-(21年-09月-16日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -41156,7 +41156,7 @@
           <t>F | 604呎 (2房)
 $1755万
 $29,060/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41171,7 +41171,7 @@
           <t>A | 955呎 (3房)
 $3559万
 $37,263/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -41179,7 +41179,7 @@
           <t>B | 842呎 (3房)
 $3067万
 $36,426/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -41187,7 +41187,7 @@
           <t>C | 850呎 (3房)
 $3166万
 $37,242/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -41195,7 +41195,7 @@
           <t>D | 920呎 (3房)
 $3252万
 $35,349/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -41203,7 +41203,7 @@
           <t>E | 341呎 (1房)
 $1176万
 $34,494/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -41211,7 +41211,7 @@
           <t>F | 604呎 (2房)
 $1750万
 $28,973/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
           <t>A | 955呎 (3房)
 $3711万
 $38,854/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -41234,7 +41234,7 @@
           <t>B | 842呎 (3房)
 $3046万
 $36,172/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -41242,7 +41242,7 @@
           <t>C | 850呎 (3房)
 $3301万
 $38,834/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>D | 921呎 (3房)
 $3230万
 $35,066/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -41258,7 +41258,7 @@
           <t>E | 341呎 (1房)
 $1173万
 $34,391/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -41266,7 +41266,7 @@
           <t>F | 604呎 (2房)
 $2083万
 $34,490/呎
-(22年-02月-24日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -41281,7 +41281,7 @@
           <t>A | 955呎 (3房)
 $3711万
 $38,854/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41289,7 +41289,7 @@
           <t>B | 842呎 (3房)
 $3046万
 $36,172/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -41297,7 +41297,7 @@
           <t>C | 850呎 (3房)
 $3301万
 $38,834/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -41305,7 +41305,7 @@
           <t>D | 921呎 (3房)
 $3341万
 $36,275/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -41313,7 +41313,7 @@
           <t>E | 341呎 (1房)
 $949万
 $27,820/呎
-(24年-02月-06日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -41321,7 +41321,7 @@
           <t>F | 604呎 (2房)
 $1719万
 $28,458/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41336,7 @@
           <t>A | 955呎 (3房)
 $3485万
 $36,493/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -41344,7 +41344,7 @@
           <t>B | 842呎 (3房)
 $3004万
 $35,673/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -41352,7 +41352,7 @@
           <t>C | 850呎 (3房)
 $3100万
 $36,473/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -41360,7 +41360,7 @@
           <t>D | 921呎 (3房)
 $3295万
 $35,774/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -41368,7 +41368,7 @@
           <t>E | 341呎 (1房)
 $1126万
 $33,021/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -41376,7 +41376,7 @@
           <t>F | 604呎 (2房)
 $1745万
 $28,899/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41391,7 +41391,7 @@
           <t>A | 955呎 (3房)
 $3356万
 $35,141/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -41399,7 +41399,7 @@
           <t>B | 842呎 (3房)
 $3132万
 $37,196/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -41407,7 +41407,7 @@
           <t>C | 850呎 (3房)
 $2950万
 $34,706/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -41415,7 +41415,7 @@
           <t>D | 921呎 (3房)
 $2993万
 $32,493/呎
-(24年-02月-19日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -41423,7 +41423,7 @@
           <t>E | 341呎 (1房)
 $1123万
 $32,922/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -41431,7 +41431,7 @@
           <t>F | 604呎 (2房)
 $1703万
 $28,203/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41446,7 +41446,7 @@
           <t>A | 955呎 (3房)
 $3403万
 $35,632/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -41454,7 +41454,7 @@
           <t>B | 842呎 (3房)
 $3025万
 $35,921/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -41462,7 +41462,7 @@
           <t>C | 850呎 (3房)
 $3122万
 $36,728/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -41470,7 +41470,7 @@
           <t>D | 921呎 (3房)
 $3185万
 $34,584/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -41478,7 +41478,7 @@
           <t>E | 341呎 (1房)
 $1147万
 $33,644/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -41486,7 +41486,7 @@
           <t>F | 604呎 (2房)
 $1698万
 $28,120/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -41501,7 +41501,7 @@
           <t>A | 955呎 (3房)
 $3558万
 $37,253/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>B | 842呎 (3房)
 $2780万
 $33,017/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -41517,7 +41517,7 @@
           <t>C | 850呎 (3房)
 $3088万
 $36,328/呎
-(21年-09月-17日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -41525,7 +41525,7 @@
           <t>D | 920呎 (3房)
 $2922万
 $31,761/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -41533,7 +41533,7 @@
           <t>E | 341呎 (1房)
 $1116万
 $32,727/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -41541,7 +41541,7 @@
           <t>F | 604呎 (2房)
 $2123万
 $35,149/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -41556,7 +41556,7 @@
           <t>A | 955呎 (3房)
 $3619万
 $37,897/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -41564,7 +41564,7 @@
           <t>B | 842呎 (3房)
 $3036万
 $36,051/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -41572,7 +41572,7 @@
           <t>C | 850呎 (3房)
 $3066万
 $36,075/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -41580,7 +41580,7 @@
           <t>D | 920呎 (3房)
 $2992万
 $32,517/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -41588,7 +41588,7 @@
           <t>E | 341呎 (1房)
 $1113万
 $32,629/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -41596,7 +41596,7 @@
           <t>F | 604呎 (2房)
 $2016万
 $33,374/呎
-(22年-07月-11日)</t>
+(22年-07月)</t>
         </is>
       </c>
     </row>
@@ -41611,7 +41611,7 @@
           <t>A | 955呎 (3房)
 $3423万
 $35,841/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -41619,7 +41619,7 @@
           <t>B | 842呎 (3房)
 $2843万
 $33,761/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -41627,7 +41627,7 @@
           <t>C | 850呎 (3房)
 $3045万
 $35,825/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -41635,7 +41635,7 @@
           <t>D | 921呎 (3房)
 $3045万
 $33,063/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -41643,7 +41643,7 @@
           <t>E | 341呎 (1房)
 $1144万
 $33,547/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -41651,7 +41651,7 @@
           <t>F | 604呎 (2房)
 $1683万
 $27,867/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -41666,7 +41666,7 @@
           <t>A | 955呎 (3房)
 $3399万
 $35,592/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -41674,7 +41674,7 @@
           <t>B | 842呎 (3房)
 $2823万
 $33,527/呎
-(23年-07月-20日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -41682,7 +41682,7 @@
           <t>C | 850呎 (3房)
 $3175万
 $37,354/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -41690,7 +41690,7 @@
           <t>D | 920呎 (3房)
 $2950万
 $32,066/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -41698,7 +41698,7 @@
           <t>E | 341呎 (1房)
 $1106万
 $32,434/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -41706,7 +41706,7 @@
           <t>F | 604呎 (2房)
 $1678万
 $27,785/呎
-(24年-01月-09日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -41721,7 +41721,7 @@
           <t>A | 955呎 (3房)
 $3363万
 $35,218/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -41729,7 +41729,7 @@
           <t>B | 842呎 (3房)
 $2683万
 $31,860/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -41737,7 +41737,7 @@
           <t>C | 850呎 (3房)
 $2994万
 $35,229/呎
-(21年-09月-16日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -41745,7 +41745,7 @@
           <t>D | 921呎 (3房)
 $2935万
 $31,872/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -41753,7 +41753,7 @@
           <t>E | 341呎 (1房)
 $1103万
 $32,335/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -41761,7 +41761,7 @@
           <t>F | 604呎 (2房)
 $1998万
 $33,075/呎
-(21年-11月-21日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -41776,7 +41776,7 @@
           <t>A | 955呎 (3房)
 $3107万
 $32,534/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -41784,7 +41784,7 @@
           <t>B | 842呎 (3房)
 $2817万
 $33,453/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -41792,7 +41792,7 @@
           <t>C | 850呎 (3房)
 $2994万
 $35,229/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -41800,7 +41800,7 @@
           <t>D | 921呎 (3房)
 $3082万
 $33,466/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -41808,7 +41808,7 @@
           <t>E | 341呎 (1房)
 $1158万
 $33,952/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -41816,7 +41816,7 @@
           <t>F | 604呎 (2房)
 $1998万
 $33,075/呎
-(22年-01月-24日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -41831,7 +41831,7 @@
           <t>A | 955呎 (3房)
 $3330万
 $34,868/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -41839,7 +41839,7 @@
           <t>B | 842呎 (3房)
 $2566万
 $30,476/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -41847,7 +41847,7 @@
           <t>C | 850呎 (3房)
 $2965万
 $34,879/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -41855,7 +41855,7 @@
           <t>D | 920呎 (3房)
 $2906万
 $31,591/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -41863,7 +41863,7 @@
           <t>E | 341呎 (1房)
 $918万
 $26,920/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -41871,7 +41871,7 @@
           <t>F | 604呎 (2房)
 $1663万
 $27,537/呎
-(24年-02月-05日)</t>
+(24年-02月)</t>
         </is>
       </c>
     </row>
@@ -41886,7 +41886,7 @@
           <t>A | 955呎 (3房)
 $3156万
 $33,042/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -41894,7 +41894,7 @@
           <t>B | 842呎 (3房)
 $2632万
 $31,264/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -41902,7 +41902,7 @@
           <t>C | 850呎 (3房)
 $2809万
 $33,052/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -41910,7 +41910,7 @@
           <t>D | 921呎 (3房)
 $3037万
 $32,970/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -41918,7 +41918,7 @@
           <t>E | 341呎 (1房)
 $1147万
 $33,649/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -41926,7 +41926,7 @@
           <t>F | 604呎 (2房)
 $1658万
 $27,453/呎
-(23年-12月-14日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -41941,7 +41941,7 @@
           <t>A | 955呎 (3房)
 $3297万
 $34,522/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -41949,7 +41949,7 @@
           <t>B | 842呎 (3房)
 $2619万
 $31,108/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -41957,7 +41957,7 @@
           <t>C | 850呎 (3房)
 $2795万
 $32,887/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -41965,7 +41965,7 @@
           <t>D | 921呎 (3房)
 $2878万
 $31,243/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -41973,7 +41973,7 @@
           <t>E | 341呎 (1房)
 $1090万
 $31,953/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -41981,7 +41981,7 @@
           <t>F | 604呎 (2房)
 $1653万
 $27,371/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -41996,7 +41996,7 @@
           <t>A | 955呎 (3房)
 $3037万
 $31,797/呎
-(24年-02月-08日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -42004,7 +42004,7 @@
           <t>B | 842呎 (3房)
 $2606万
 $30,953/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -42012,7 +42012,7 @@
           <t>C | 850呎 (3房)
 $2926万
 $34,428/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -42020,7 +42020,7 @@
           <t>D | 921呎 (3房)
 $2869万
 $31,150/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -42028,7 +42028,7 @@
           <t>E | 341呎 (1房)
 $1086万
 $31,859/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -42036,7 +42036,7 @@
           <t>F | 604呎 (2房)
 $2067万
 $34,215/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -42051,7 +42051,7 @@
           <t>A | 955呎 (3房)
 $3027万
 $31,701/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -42059,7 +42059,7 @@
           <t>B | 842呎 (3房)
 $2593万
 $30,798/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -42067,7 +42067,7 @@
           <t>C | 850呎 (3房)
 $2918万
 $34,325/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -42075,7 +42075,7 @@
           <t>D | 921呎 (3房)
 $2860万
 $31,057/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -42083,7 +42083,7 @@
           <t>E | 341呎 (1房)
 $1130万
 $33,150/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -42091,7 +42091,7 @@
           <t>F | 604呎 (2房)
 $1643万
 $27,208/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42106,7 +42106,7 @@
           <t>A | 955呎 (3房)
 $3267万
 $34,212/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -42114,7 +42114,7 @@
           <t>B | 842呎 (3房)
 $2654万
 $31,516/呎
-(22年-06月-27日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -42122,7 +42122,7 @@
           <t>C | 850呎 (3房)
 $2909万
 $34,223/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -42130,7 +42130,7 @@
           <t>D | 921呎 (3房)
 $2852万
 $30,963/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -42138,7 +42138,7 @@
           <t>E | 341呎 (1房)
 $1127万
 $33,048/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -42146,7 +42146,7 @@
           <t>F | 604呎 (2房)
 $2054万
 $34,010/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -42161,7 +42161,7 @@
           <t>A | 955呎 (3房)
 $3112万
 $32,583/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -42169,7 +42169,7 @@
           <t>B | 842呎 (3房)
 $2709万
 $32,178/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -42177,7 +42177,7 @@
           <t>C | 850呎 (3房)
 $2770万
 $32,593/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -42185,7 +42185,7 @@
           <t>D | 921呎 (3房)
 $2923万
 $31,737/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -42193,7 +42193,7 @@
           <t>E | 341呎 (1房)
 $1134万
 $33,253/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -42201,7 +42201,7 @@
           <t>F | 604呎 (2房)
 $1634万
 $27,046/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -42216,7 +42216,7 @@
           <t>A | 955呎 (3房)
 $3248万
 $34,008/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42224,7 +42224,7 @@
           <t>B | 842呎 (3房)
 $2635万
 $31,291/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -42232,7 +42232,7 @@
           <t>C | 850呎 (3房)
 $2754万
 $32,398/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -42240,7 +42240,7 @@
           <t>D | 920呎 (3房)
 $2835万
 $30,810/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -42248,7 +42248,7 @@
           <t>E | 341呎 (1房)
 $1127万
 $33,056/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -42256,7 +42256,7 @@
           <t>F | 604呎 (2房)
 $1624万
 $26,885/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -42271,7 +42271,7 @@
           <t>A | 955呎 (3房)
 $3084万
 $32,291/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42279,7 +42279,7 @@
           <t>B | 842呎 (3房)
 $2606万
 $30,948/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -42287,7 +42287,7 @@
           <t>C | 850呎 (3房)
 $2746万
 $32,301/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -42295,7 +42295,7 @@
           <t>D | 921呎 (3房)
 $2826万
 $30,685/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -42303,7 +42303,7 @@
           <t>E | 341呎 (1房)
 $1070万
 $31,385/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -42311,7 +42311,7 @@
           <t>F | 604呎 (2房)
 $1619万
 $26,804/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -42326,7 +42326,7 @@
           <t>A | 901呎 (3房)
 $3244万
 $36,000/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -42334,7 +42334,7 @@
           <t>B | 797呎 (3房)
 $2778万
 $34,851/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -42342,7 +42342,7 @@
           <t>C | 799呎 (3房)
 $2916万
 $36,500/呎
-(22年-02月-08日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -42350,7 +42350,7 @@
           <t>D | 873呎 (3房)
 $3250万
 $37,232/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -42358,7 +42358,7 @@
           <t>E | 320呎 (1房)
 $841万
 $26,287/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -42366,7 +42366,7 @@
           <t>F | 566呎 (2房)
 $1840万
 $32,500/呎
-(22年-04月-13日)</t>
+(22年-04月)</t>
         </is>
       </c>
     </row>
@@ -42523,7 +42523,7 @@
           <t>B | 1431呎 (4+房)
 $6053万
 $42,300/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -42542,10 +42542,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -42553,61 +42602,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月-25日)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月-26日)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -42620,7 +42620,7 @@
           <t>A | 638呎 (2房)
 $2180万
 $34,170/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -42628,7 +42628,7 @@
           <t>B | 594呎 (2房)
 $1673万
 $28,166/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -42636,7 +42636,7 @@
           <t>C | 749呎 (3房)
 $2405万
 $32,115/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr"/>
@@ -42645,7 +42645,7 @@
           <t>E | 553呎 (2房)
 $2008万
 $36,302/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -42653,7 +42653,7 @@
           <t>F | 343呎 (1房)
 $1273万
 $37,124/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -42661,7 +42661,7 @@
           <t>G | 470呎 (2房)
 $1702万
 $36,208/呎
-(22年-05月-25日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -42676,7 +42676,7 @@
           <t>A | 638呎 (2房)
 $2070万
 $32,446/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -42684,7 +42684,7 @@
           <t>B | 594呎 (2房)
 $1946万
 $32,761/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -42692,7 +42692,7 @@
           <t>C | 749呎 (3房)
 $2398万
 $32,021/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr"/>
@@ -42701,7 +42701,7 @@
           <t>E | 553呎 (2房)
 $2002万
 $36,195/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -42709,7 +42709,7 @@
           <t>F | 343呎 (1房)
 $1270万
 $37,014/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -42717,7 +42717,7 @@
           <t>G | 470呎 (2房)
 $1697万
 $36,099/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -42732,7 +42732,7 @@
           <t>A | 638呎 (2房)
 $2063万
 $32,335/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -42740,7 +42740,7 @@
           <t>B | 594呎 (2房)
 $1931万
 $32,504/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -42748,7 +42748,7 @@
           <t>C | 749呎 (3房)
 $2391万
 $31,925/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr"/>
@@ -42757,7 +42757,7 @@
           <t>E | 553呎 (2房)
 $1996万
 $36,088/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -42765,7 +42765,7 @@
           <t>F | 343呎 (1房)
 $1266万
 $36,904/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -42773,7 +42773,7 @@
           <t>G | 470呎 (2房)
 $1776万
 $37,791/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -42788,7 +42788,7 @@
           <t>A | 638呎 (2房)
 $2057万
 $32,237/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -42796,7 +42796,7 @@
           <t>B | 594呎 (2房)
 $1833万
 $30,865/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -42804,7 +42804,7 @@
           <t>C | 749呎 (3房)
 $2384万
 $31,828/呎
-(23年-12月-20日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr"/>
@@ -42813,7 +42813,7 @@
           <t>E | 553呎 (2房)
 $1895万
 $34,265/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -42821,7 +42821,7 @@
           <t>F | 343呎 (1房)
 $1202万
 $35,039/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -42829,7 +42829,7 @@
           <t>G | 470呎 (2房)
 $1687万
 $35,884/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -42844,7 +42844,7 @@
           <t>A | 638呎 (2房)
 $1953万
 $30,609/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -42852,7 +42852,7 @@
           <t>B | 594呎 (2房)
 $1828万
 $30,770/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -42860,7 +42860,7 @@
           <t>C | 749呎 (3房)
 $2377万
 $31,733/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -42869,7 +42869,7 @@
           <t>E | 553呎 (2房)
 $1889万
 $34,164/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -42877,7 +42877,7 @@
           <t>F | 343呎 (1房)
 $1004万
 $29,259/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -42885,7 +42885,7 @@
           <t>G | 470呎 (2房)
 $1408万
 $29,963/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -42900,7 +42900,7 @@
           <t>A | 638呎 (2房)
 $1947万
 $30,519/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -42908,7 +42908,7 @@
           <t>B | 594呎 (2房)
 $1640万
 $27,611/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -42916,7 +42916,7 @@
           <t>C | 749呎 (3房)
 $2971万
 $39,666/呎
-(22年-01月-21日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -42925,7 +42925,7 @@
           <t>E | 553呎 (2房)
 $1884万
 $34,063/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -42933,7 +42933,7 @@
           <t>F | 343呎 (1房)
 $1254万
 $36,573/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -42941,7 +42941,7 @@
           <t>G | 470呎 (2房)
 $1404万
 $29,874/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -42956,7 +42956,7 @@
           <t>A | 638呎 (2房)
 $1941万
 $30,428/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -42964,7 +42964,7 @@
           <t>B | 594呎 (2房)
 $1908万
 $32,117/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -42972,7 +42972,7 @@
           <t>C | 749呎 (3房)
 $2363万
 $31,545/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -42981,7 +42981,7 @@
           <t>E | 553呎 (2房)
 $1878万
 $33,959/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -42989,7 +42989,7 @@
           <t>F | 343呎 (1房)
 $1251万
 $36,465/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -42997,7 +42997,7 @@
           <t>G | 470呎 (2房)
 $1400万
 $29,784/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -43012,7 +43012,7 @@
           <t>A | 638呎 (2房)
 $1913万
 $29,979/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -43020,7 +43020,7 @@
           <t>B | 594呎 (2房)
 $1861万
 $31,329/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -43028,7 +43028,7 @@
           <t>C | 749呎 (3房)
 $2339万
 $31,223/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -43037,7 +43037,7 @@
           <t>E | 553呎 (2房)
 $1850万
 $33,458/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -43045,7 +43045,7 @@
           <t>F | 343呎 (1房)
 $1174万
 $34,216/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -43053,7 +43053,7 @@
           <t>G | 470呎 (2房)
 $1647万
 $35,038/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43068,7 +43068,7 @@
           <t>A | 638呎 (2房)
 $1996万
 $31,289/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -43076,7 +43076,7 @@
           <t>B | 594呎 (2房)
 $1762万
 $29,661/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -43084,7 +43084,7 @@
           <t>C | 749呎 (3房)
 $2673万
 $35,686/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -43093,7 +43093,7 @@
           <t>E | 553呎 (2房)
 $1839万
 $33,257/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -43101,7 +43101,7 @@
           <t>F | 343呎 (1房)
 $977万
 $28,484/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -43109,7 +43109,7 @@
           <t>G | 470呎 (2房)
 $1637万
 $34,829/呎
-(22年-05月-23日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -43124,7 +43124,7 @@
           <t>A | 638呎 (2房)
 $1990万
 $31,197/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -43132,7 +43132,7 @@
           <t>B | 594呎 (2房)
 $1844万
 $31,049/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -43140,7 +43140,7 @@
           <t>C | 749呎 (3房)
 $2665万
 $35,579/呎
-(21年-09月-17日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -43149,7 +43149,7 @@
           <t>E | 553呎 (2房)
 $1925万
 $34,815/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -43157,7 +43157,7 @@
           <t>F | 343呎 (1房)
 $1221万
 $35,603/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -43165,7 +43165,7 @@
           <t>G | 470呎 (2房)
 $1632万
 $34,725/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43180,7 +43180,7 @@
           <t>A | 638呎 (2房)
 $1965万
 $30,797/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43188,7 +43188,7 @@
           <t>B | 594呎 (2房)
 $1839万
 $30,957/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -43196,7 +43196,7 @@
           <t>C | 749呎 (3房)
 $2723万
 $36,359/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -43205,7 +43205,7 @@
           <t>E | 553呎 (2房)
 $1828万
 $33,060/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -43213,7 +43213,7 @@
           <t>F | 343呎 (1房)
 $1160万
 $33,808/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -43221,7 +43221,7 @@
           <t>G | 470呎 (2房)
 $1627万
 $34,620/呎
-(22年-01月-20日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -43236,7 +43236,7 @@
           <t>A | 638呎 (2房)
 $1866万
 $29,243/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43244,7 +43244,7 @@
           <t>B | 594呎 (2房)
 $1746万
 $29,395/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -43252,7 +43252,7 @@
           <t>C | 749呎 (3房)
 $2649万
 $35,367/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -43261,7 +43261,7 @@
           <t>E | 553呎 (2房)
 $1823万
 $32,961/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -43269,7 +43269,7 @@
           <t>F | 343呎 (1房)
 $1214万
 $35,393/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -43277,7 +43277,7 @@
           <t>G | 470呎 (2房)
 $1622万
 $34,517/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43292,7 +43292,7 @@
           <t>A | 638呎 (2房)
 $1860万
 $29,155/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -43300,7 +43300,7 @@
           <t>B | 594呎 (2房)
 $1795万
 $30,224/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -43308,7 +43308,7 @@
           <t>C | 749呎 (3房)
 $2641万
 $35,262/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -43317,7 +43317,7 @@
           <t>E | 553呎 (2房)
 $1800万
 $32,547/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -43325,7 +43325,7 @@
           <t>F | 343呎 (1房)
 $1210万
 $35,290/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -43333,7 +43333,7 @@
           <t>G | 470呎 (2房)
 $1668万
 $35,489/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43348,7 +43348,7 @@
           <t>A | 638呎 (2房)
 $1854万
 $29,067/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43356,7 +43356,7 @@
           <t>B | 594呎 (2房)
 $1736万
 $29,219/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -43364,7 +43364,7 @@
           <t>C | 749呎 (3房)
 $2765万
 $36,912/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -43373,7 +43373,7 @@
           <t>E | 553呎 (2房)
 $1615万
 $29,205/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -43381,7 +43381,7 @@
           <t>F | 343呎 (1房)
 $963万
 $28,064/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -43389,7 +43389,7 @@
           <t>G | 470呎 (2房)
 $1693万
 $36,027/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43404,7 +43404,7 @@
           <t>A | 638呎 (2房)
 $1849万
 $28,979/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43412,7 +43412,7 @@
           <t>B | 594呎 (2房)
 $1817万
 $30,588/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -43420,7 +43420,7 @@
           <t>C | 749呎 (3房)
 $2625万
 $35,050/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr"/>
@@ -43429,7 +43429,7 @@
           <t>E | 553呎 (2房)
 $1879万
 $33,971/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -43437,7 +43437,7 @@
           <t>F | 343呎 (1房)
 $1146万
 $33,406/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -43445,7 +43445,7 @@
           <t>G | 470呎 (2房)
 $1688万
 $35,920/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43460,7 +43460,7 @@
           <t>A | 638呎 (2房)
 $1936万
 $30,339/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43468,7 +43468,7 @@
           <t>B | 594呎 (2房)
 $1725万
 $29,045/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -43476,7 +43476,7 @@
           <t>C | 749呎 (3房)
 $2617万
 $34,946/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr"/>
@@ -43485,7 +43485,7 @@
           <t>E | 553呎 (2房)
 $1784万
 $32,255/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -43493,7 +43493,7 @@
           <t>F | 343呎 (1房)
 $1142万
 $33,308/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -43501,7 +43501,7 @@
           <t>G | 470呎 (2房)
 $1343万
 $28,565/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -43516,7 +43516,7 @@
           <t>A | 638呎 (2房)
 $1843万
 $28,894/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43524,7 +43524,7 @@
           <t>B | 594呎 (2房)
 $1779万
 $29,953/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -43532,7 +43532,7 @@
           <t>C | 749呎 (3房)
 $2748万
 $36,693/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -43541,7 +43541,7 @@
           <t>E | 553呎 (2房)
 $1784万
 $32,255/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -43549,7 +43549,7 @@
           <t>F | 343呎 (1房)
 $1142万
 $33,308/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -43557,7 +43557,7 @@
           <t>G | 470呎 (2房)
 $1653万
 $35,173/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43572,7 +43572,7 @@
           <t>A | 638呎 (2房)
 $1832万
 $28,721/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -43580,7 +43580,7 @@
           <t>B | 594呎 (2房)
 $1715万
 $28,873/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -43588,7 +43588,7 @@
           <t>C | 749呎 (3房)
 $2602万
 $34,736/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr"/>
@@ -43597,7 +43597,7 @@
           <t>E | 553呎 (2房)
 $1773万
 $32,062/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -43605,7 +43605,7 @@
           <t>F | 343呎 (1房)
 $1136万
 $33,108/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -43613,7 +43613,7 @@
           <t>G | 470呎 (2房)
 $1593万
 $33,903/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43628,7 +43628,7 @@
           <t>A | 638呎 (2房)
 $1873万
 $29,350/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -43636,7 +43636,7 @@
           <t>B | 594呎 (2房)
 $1753万
 $29,506/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -43644,7 +43644,7 @@
           <t>C | 749呎 (3房)
 $2724万
 $36,364/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr"/>
@@ -43653,7 +43653,7 @@
           <t>E | 553呎 (2房)
 $1591万
 $28,770/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -43661,7 +43661,7 @@
           <t>F | 343呎 (1房)
 $1132万
 $33,008/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -43669,7 +43669,7 @@
           <t>G | 470呎 (2房)
 $1330万
 $28,308/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -43684,7 +43684,7 @@
           <t>A | 638呎 (2房)
 $1867万
 $29,263/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -43692,7 +43692,7 @@
           <t>B | 594呎 (2房)
 $1790万
 $30,135/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -43700,7 +43700,7 @@
           <t>C | 749呎 (3房)
 $2586万
 $34,529/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr"/>
@@ -43709,7 +43709,7 @@
           <t>E | 553呎 (2房)
 $1851万
 $33,463/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -43717,7 +43717,7 @@
           <t>F | 343呎 (1房)
 $1157万
 $33,732/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -43725,7 +43725,7 @@
           <t>G | 470呎 (2房)
 $1584万
 $33,699/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43740,7 +43740,7 @@
           <t>A | 638呎 (2房)
 $1861万
 $29,176/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -43748,7 +43748,7 @@
           <t>B | 594呎 (2房)
 $1700万
 $28,614/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -43756,7 +43756,7 @@
           <t>C | 749呎 (3房)
 $2707万
 $36,148/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr"/>
@@ -43765,7 +43765,7 @@
           <t>E | 553呎 (2房)
 $1757万
 $31,776/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -43773,7 +43773,7 @@
           <t>F | 343呎 (1房)
 $1125万
 $32,809/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -43781,7 +43781,7 @@
           <t>G | 470呎 (2房)
 $1579万
 $33,598/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
           <t>A | 638呎 (2房)
 $1901万
 $29,799/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -43804,7 +43804,7 @@
           <t>B | 594呎 (2房)
 $1525万
 $25,674/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -43812,7 +43812,7 @@
           <t>C | 749呎 (3房)
 $2699万
 $36,040/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr"/>
@@ -43821,7 +43821,7 @@
           <t>E | 553呎 (2房)
 $1752万
 $31,680/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -43829,7 +43829,7 @@
           <t>F | 343呎 (1房)
 $1122万
 $32,714/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -43837,7 +43837,7 @@
           <t>G | 470呎 (2房)
 $1574万
 $33,500/呎
-(22年-02月-15日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -43852,7 +43852,7 @@
           <t>A | 638呎 (2房)
 $1895万
 $29,709/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -43860,7 +43860,7 @@
           <t>B | 594呎 (2房)
 $1690万
 $28,443/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -43868,7 +43868,7 @@
           <t>C | 749呎 (3房)
 $2691万
 $35,932/呎
-(21年-09月-17日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr"/>
@@ -43877,7 +43877,7 @@
           <t>E | 553呎 (2房)
 $1834万
 $33,164/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -43885,7 +43885,7 @@
           <t>F | 343呎 (1房)
 $1175万
 $34,249/呎
-(22年-02月-21日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -43893,7 +43893,7 @@
           <t>G | 470呎 (2房)
 $1315万
 $27,972/呎
-(23年-12月-17日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -43908,7 +43908,7 @@
           <t>A | 638呎 (2房)
 $1895万
 $29,709/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -43916,7 +43916,7 @@
           <t>B | 544呎 (2房)
 $1578万
 $29,012/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -43924,7 +43924,7 @@
           <t>C | 469呎 (2房)
 $1491万
 $31,792/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -43932,7 +43932,7 @@
           <t>D | 335呎 (1房)
 $1158万
 $34,553/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -43940,7 +43940,7 @@
           <t>E | 553呎 (2房)
 $1572万
 $28,426/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -43948,7 +43948,7 @@
           <t>F | 343呎 (1房)
 $934万
 $27,238/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -43956,7 +43956,7 @@
           <t>G | 470呎 (2房)
 $1311万
 $27,888/呎
-(24年-02月-20日)</t>
+(24年-02月)</t>
         </is>
       </c>
     </row>
@@ -43971,7 +43971,7 @@
           <t>A | 638呎 (2房)
 $1794万
 $28,125/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -43979,7 +43979,7 @@
           <t>B | 544呎 (2房)
 $1647万
 $30,280/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -43987,7 +43987,7 @@
           <t>C | 470呎 (2房)
 $1556万
 $33,110/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -43995,7 +43995,7 @@
           <t>D | 335呎 (1房)
 $913万
 $27,262/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -44003,7 +44003,7 @@
           <t>E | 553呎 (2房)
 $1766万
 $31,931/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -44011,7 +44011,7 @@
           <t>F | 343呎 (1房)
 $1103万
 $32,170/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -44019,7 +44019,7 @@
           <t>G | 470呎 (2房)
 $1303万
 $27,722/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44034,7 +44034,7 @@
           <t>A | 638呎 (2房)
 $1610万
 $25,236/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -44042,7 +44042,7 @@
           <t>B | 545呎 (2房)
 $1642万
 $30,134/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -44050,7 +44050,7 @@
           <t>C | 469呎 (2房)
 $1478万
 $31,509/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -44058,7 +44058,7 @@
           <t>D | 335呎 (1房)
 $1110万
 $33,143/呎
-(21年-09月-10日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -44066,7 +44066,7 @@
           <t>E | 553呎 (2房)
 $1531万
 $27,680/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -44074,7 +44074,7 @@
           <t>F | 343呎 (1房)
 $1144万
 $33,348/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -44082,7 +44082,7 @@
           <t>G | 470呎 (2房)
 $1299万
 $27,638/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -44097,7 +44097,7 @@
           <t>A | 598呎 (2房)
 $2003万
 $33,500/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -44105,7 +44105,7 @@
           <t>B | 506呎 (2房)
 $1594万
 $31,500/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -44113,7 +44113,7 @@
           <t>C | 436呎 (2房)
 $1405万
 $32,226/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr"/>
@@ -44124,7 +44124,7 @@
           <t>G | 442呎 (2房)
 $1222万
 $27,637/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -38131,7 +38131,7 @@
           <t>A | 1848呎 (4+房)
 $13900万
 $75,216/呎
-(22年-02月)</t>
+(22年-02月-20日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -38139,7 +38139,7 @@
           <t>B | 1102呎 (3房)
 $4972万
 $45,120/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -38165,7 +38165,7 @@
           <t>B | 934呎 (3房)
 $4522万
 $48,415/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -38173,7 +38173,7 @@
           <t>C | 524呎 (2房)
 $1872万
 $35,730/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -38181,7 +38181,7 @@
           <t>D | 751呎 (3房)
 $2360万
 $31,431/呎
-(23年-12月)</t>
+(23年-12月-26日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -38189,7 +38189,7 @@
           <t>E | 496呎 (2房)
 $1800万
 $36,293/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -38212,7 +38212,7 @@
           <t>B | 934呎 (3房)
 $4477万
 $47,936/呎
-(22年-02月)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -38220,7 +38220,7 @@
           <t>C | 524呎 (2房)
 $1867万
 $35,623/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -38228,7 +38228,7 @@
           <t>D | 751呎 (3房)
 $2769万
 $36,867/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -38236,7 +38236,7 @@
           <t>E | 496呎 (2房)
 $1795万
 $36,184/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -38251,7 +38251,7 @@
           <t>A | 1299呎 (4+房)
 $7469万
 $57,500/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -38259,7 +38259,7 @@
           <t>B | 934呎 (3房)
 $4167万
 $44,615/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -38267,7 +38267,7 @@
           <t>C | 524呎 (2房)
 $1861万
 $35,518/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -38275,7 +38275,7 @@
           <t>D | 751呎 (3房)
 $2312万
 $30,784/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -38283,7 +38283,7 @@
           <t>E | 496呎 (2房)
 $1789万
 $36,076/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
           <t>A | 1299呎 (4+房)
 $6300万
 $48,499/呎
-(23年-04月)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -38306,7 +38306,7 @@
           <t>B | 934呎 (3房)
 $4360万
 $46,681/呎
-(23年-04月)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -38314,7 +38314,7 @@
           <t>C | 524呎 (2房)
 $1925万
 $36,740/呎
-(21年-11月)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -38322,7 +38322,7 @@
           <t>D | 751呎 (3房)
 $2760万
 $36,758/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -38330,7 +38330,7 @@
           <t>E | 496呎 (2房)
 $1511万
 $30,465/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -38345,7 +38345,7 @@
           <t>A | 1299呎 (4+房)
 $6174万
 $47,530/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -38353,7 +38353,7 @@
           <t>B | 934呎 (3房)
 $4282万
 $45,843/呎
-(23年-02月)</t>
+(23年-02月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -38361,7 +38361,7 @@
           <t>C | 524呎 (2房)
 $1866万
 $35,605/呎
-(23年-05月)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -38369,7 +38369,7 @@
           <t>D | 751呎 (3房)
 $2613万
 $34,798/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>E | 496呎 (2房)
 $1669万
 $33,647/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -38392,7 +38392,7 @@
           <t>A | 1299呎 (4+房)
 $6240万
 $48,037/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -38400,7 +38400,7 @@
           <t>B | 934呎 (3房)
 $4278万
 $45,798/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -38408,7 +38408,7 @@
           <t>C | 524呎 (2房)
 $1817万
 $34,678/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -38416,7 +38416,7 @@
           <t>D | 751呎 (3房)
 $2736万
 $36,429/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -38424,7 +38424,7 @@
           <t>E | 496呎 (2房)
 $1664万
 $33,547/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -38439,7 +38439,7 @@
           <t>A | 1299呎 (4+房)
 $6180万
 $47,575/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -38447,7 +38447,7 @@
           <t>B | 934呎 (3房)
 $4235万
 $45,345/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -38455,7 +38455,7 @@
           <t>C | 524呎 (2房)
 $1812万
 $34,573/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -38463,7 +38463,7 @@
           <t>D | 751呎 (3房)
 $2728万
 $36,320/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -38471,7 +38471,7 @@
           <t>E | 496呎 (2房)
 $1659万
 $33,445/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -38486,7 +38486,7 @@
           <t>A | 1299呎 (4+房)
 $6138万
 $47,252/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -38494,7 +38494,7 @@
           <t>B | 934呎 (3房)
 $4193万
 $44,896/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -38502,7 +38502,7 @@
           <t>C | 524呎 (2房)
 $1806万
 $34,470/呎
-(23年-05月)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -38510,7 +38510,7 @@
           <t>D | 751呎 (3房)
 $2331万
 $31,039/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -38518,7 +38518,7 @@
           <t>E | 496呎 (2房)
 $1694万
 $34,159/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
           <t>A | 1299呎 (4+房)
 $5716万
 $44,004/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -38541,7 +38541,7 @@
           <t>B | 934呎 (3房)
 $3954万
 $42,334/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -38549,7 +38549,7 @@
           <t>C | 524呎 (2房)
 $1508万
 $28,783/呎
-(24年-02月)</t>
+(24年-02月-19日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -38557,7 +38557,7 @@
           <t>D | 751呎 (3房)
 $2711万
 $36,103/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -38565,7 +38565,7 @@
           <t>E | 496呎 (2房)
 $1689万
 $34,057/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -38580,7 +38580,7 @@
           <t>A | 1299呎 (4+房)
 $5328万
 $41,016/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -38588,7 +38588,7 @@
           <t>B | 934呎 (3房)
 $4016万
 $43,000/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -38596,7 +38596,7 @@
           <t>C | 524呎 (2房)
 $1885万
 $35,979/呎
-(21年-10月)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -38604,7 +38604,7 @@
           <t>D | 751呎 (3房)
 $2655万
 $35,353/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -38612,7 +38612,7 @@
           <t>E | 496呎 (2房)
 $1604万
 $32,339/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
     </row>
@@ -38627,7 +38627,7 @@
           <t>A | 1299呎 (4+房)
 $5680万
 $43,726/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -38635,7 +38635,7 @@
           <t>B | 934呎 (3房)
 $3960万
 $42,402/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -38643,7 +38643,7 @@
           <t>C | 524呎 (2房)
 $1880万
 $35,872/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -38651,7 +38651,7 @@
           <t>D | 751呎 (3房)
 $2695万
 $35,886/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -38659,7 +38659,7 @@
           <t>E | 497呎 (2房)
 $1639万
 $32,981/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -38674,7 +38674,7 @@
           <t>A | 1299呎 (4+房)
 $5389万
 $41,485/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -38682,7 +38682,7 @@
           <t>B | 934呎 (3房)
 $3933万
 $42,107/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -38690,7 +38690,7 @@
           <t>C | 524呎 (2房)
 $1495万
 $28,526/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -38698,7 +38698,7 @@
           <t>D | 751呎 (3房)
 $2559万
 $34,076/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -38706,7 +38706,7 @@
           <t>E | 497呎 (2房)
 $1594万
 $32,080/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
     </row>
@@ -38721,7 +38721,7 @@
           <t>A | 1299呎 (4+房)
 $5849万
 $45,030/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -38729,7 +38729,7 @@
           <t>B | 934呎 (3房)
 $4206万
 $45,029/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -38737,7 +38737,7 @@
           <t>C | 524呎 (2房)
 $1495万
 $28,526/呎
-(23年-11月)</t>
+(23年-11月-24日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -38745,7 +38745,7 @@
           <t>D | 751呎 (3房)
 $2559万
 $34,076/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -38753,7 +38753,7 @@
           <t>E | 497呎 (2房)
 $1674万
 $33,685/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -38768,7 +38768,7 @@
           <t>A | 1299呎 (4+房)
 $5164万
 $39,758/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -38776,7 +38776,7 @@
           <t>B | 934呎 (3房)
 $3951万
 $42,301/呎
-(23年-02月)</t>
+(23年-02月-19日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -38784,7 +38784,7 @@
           <t>C | 524呎 (2房)
 $1774万
 $33,858/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -38792,7 +38792,7 @@
           <t>D | 751呎 (3房)
 $2544万
 $33,874/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -38800,7 +38800,7 @@
           <t>E | 497呎 (2房)
 $1426万
 $28,700/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -38815,7 +38815,7 @@
           <t>A | 1299呎 (4+房)
 $4880万
 $37,567/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -38823,7 +38823,7 @@
           <t>B | 934呎 (3房)
 $3688万
 $39,481/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -38831,7 +38831,7 @@
           <t>C | 524呎 (2房)
 $1481万
 $28,272/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -38839,7 +38839,7 @@
           <t>D | 751呎 (3房)
 $2663万
 $35,459/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -38847,7 +38847,7 @@
           <t>E | 497呎 (2房)
 $1580万
 $31,792/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -38862,7 +38862,7 @@
           <t>A | 1299呎 (4+房)
 $5040万
 $38,800/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -38870,7 +38870,7 @@
           <t>B | 934呎 (3房)
 $3974万
 $42,549/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -38878,7 +38878,7 @@
           <t>C | 524呎 (2房)
 $1499万
 $28,609/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -38886,7 +38886,7 @@
           <t>D | 751呎 (3房)
 $2529万
 $33,669/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -38894,7 +38894,7 @@
           <t>E | 497呎 (2房)
 $1654万
 $33,286/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -38909,7 +38909,7 @@
           <t>A | 1299呎 (4+房)
 $5238万
 $40,320/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -38917,7 +38917,7 @@
           <t>B | 934呎 (3房)
 $3766万
 $40,322/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -38925,7 +38925,7 @@
           <t>C | 524呎 (2房)
 $1473万
 $28,104/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -38933,7 +38933,7 @@
           <t>D | 751呎 (3房)
 $2521万
 $33,569/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -38941,7 +38941,7 @@
           <t>E | 497呎 (2房)
 $1620万
 $32,593/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
     </row>
@@ -38956,7 +38956,7 @@
           <t>A | 1299呎 (4+房)
 $5472万
 $42,125/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -38964,7 +38964,7 @@
           <t>B | 934呎 (3房)
 $3747万
 $40,121/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -38972,7 +38972,7 @@
           <t>C | 524呎 (2房)
 $1468万
 $28,020/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -38980,7 +38980,7 @@
           <t>D | 751呎 (3房)
 $2514万
 $33,469/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -38988,7 +38988,7 @@
           <t>E | 497呎 (2房)
 $1605万
 $32,299/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -39003,7 +39003,7 @@
           <t>A | 1299呎 (4+房)
 $4875万
 $37,529/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -39011,7 +39011,7 @@
           <t>B | 934呎 (3房)
 $3505万
 $37,526/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39019,7 +39019,7 @@
           <t>C | 524呎 (2房)
 $1464万
 $27,937/呎
-(24年-03月)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -39027,7 +39027,7 @@
           <t>D | 751呎 (3房)
 $2506万
 $33,369/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -39035,7 +39035,7 @@
           <t>E | 497呎 (2房)
 $1561万
 $31,417/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -39050,7 +39050,7 @@
           <t>A | 1299呎 (4+房)
 $5365万
 $41,298/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -39058,7 +39058,7 @@
           <t>B | 934呎 (3房)
 $3674万
 $39,331/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39066,7 +39066,7 @@
           <t>C | 524呎 (2房)
 $1417万
 $27,044/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -39074,7 +39074,7 @@
           <t>D | 751呎 (3房)
 $2623万
 $34,931/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -39082,7 +39082,7 @@
           <t>E | 497呎 (2房)
 $1635万
 $32,889/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -39097,7 +39097,7 @@
           <t>A | 1299呎 (4+房)
 $4704万
 $36,216/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -39105,7 +39105,7 @@
           <t>B | 934呎 (3房)
 $3819万
 $40,888/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39113,7 +39113,7 @@
           <t>C | 524呎 (2房)
 $1409万
 $26,885/呎
-(24年-03月)</t>
+(24年-03月-07日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -39121,7 +39121,7 @@
           <t>D | 751呎 (3房)
 $2608万
 $34,723/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -39129,7 +39129,7 @@
           <t>E | 497呎 (2房)
 $1625万
 $32,693/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
           <t>A | 1299呎 (4+房)
 $4731万
 $36,423/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -39152,7 +39152,7 @@
           <t>B | 934呎 (3房)
 $3800万
 $40,685/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39160,7 +39160,7 @@
           <t>C | 524呎 (2房)
 $1405万
 $26,804/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -39168,7 +39168,7 @@
           <t>D | 751呎 (3房)
 $2476万
 $32,970/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -39176,7 +39176,7 @@
           <t>E | 497呎 (2房)
 $1620万
 $32,596/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -39191,7 +39191,7 @@
           <t>A | 1229呎 (4+房)
 $5430万
 $44,181/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -39199,7 +39199,7 @@
           <t>B | 874呎 (3房)
 $3861万
 $44,180/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39207,7 +39207,7 @@
           <t>C | 487呎 (2房)
 $1694万
 $34,778/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -39215,7 +39215,7 @@
           <t>D | 709呎 (3房)
 $2482万
 $35,000/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -39223,7 +39223,7 @@
           <t>E | 461呎 (2房)
 $1567万
 $34,001/呎
-(22年-02月)</t>
+(22年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -39373,7 +39373,7 @@
           <t>A | 1902呎 (4+房)
 $13000万
 $68,349/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -39389,7 +39389,7 @@
           <t>C | 1000呎 (3房)
 $4700万
 $47,000/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -39407,7 +39407,7 @@
           <t>A | 1420呎 (4+房)
 $8557万
 $60,260/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -39415,7 +39415,7 @@
           <t>B | 942呎 (3房)
 $4553万
 $48,334/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -39423,7 +39423,7 @@
           <t>C | 589呎 (2房)
 $1981万
 $33,630/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -39431,7 +39431,7 @@
           <t>D | 481呎 (2房)
 $1602万
 $33,314/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -39439,7 +39439,7 @@
           <t>E | 523呎 (2房)
 $1817万
 $34,733/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -39447,7 +39447,7 @@
           <t>F | 464呎 (2房)
 $1386万
 $29,861/呎
-(24年-01月)</t>
+(24年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -39470,7 +39470,7 @@
           <t>B | 942呎 (3房)
 $4095万
 $43,471/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -39478,7 +39478,7 @@
           <t>C | 589呎 (2房)
 $1975万
 $33,529/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -39486,7 +39486,7 @@
           <t>D | 481呎 (2房)
 $1678万
 $34,877/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -39494,7 +39494,7 @@
           <t>E | 523呎 (2房)
 $1806万
 $34,527/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -39502,7 +39502,7 @@
           <t>F | 464呎 (2房)
 $1698万
 $36,586/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -39517,7 +39517,7 @@
           <t>A | 1420呎 (4+房)
 $8520万
 $60,000/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -39525,7 +39525,7 @@
           <t>B | 941呎 (3房)
 $4360万
 $46,332/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -39533,7 +39533,7 @@
           <t>C | 589呎 (2房)
 $1969万
 $33,429/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -39541,7 +39541,7 @@
           <t>D | 481呎 (2房)
 $1673万
 $34,772/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -39549,7 +39549,7 @@
           <t>E | 524呎 (2房)
 $1887万
 $36,005/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -39557,7 +39557,7 @@
           <t>F | 464呎 (2房)
 $1638万
 $35,302/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -39572,7 +39572,7 @@
           <t>A | 1420呎 (4+房)
 $7025万
 $49,470/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -39580,7 +39580,7 @@
           <t>B | 942呎 (3房)
 $3651万
 $38,759/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39588,7 +39588,7 @@
           <t>C | 589呎 (2房)
 $1940万
 $32,934/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -39596,7 +39596,7 @@
           <t>D | 481呎 (2房)
 $1600万
 $33,270/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -39604,7 +39604,7 @@
           <t>E | 524呎 (2房)
 $1703万
 $32,498/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -39612,7 +39612,7 @@
           <t>F | 464呎 (2房)
 $1614万
 $34,779/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -39627,7 +39627,7 @@
           <t>A | 1420呎 (4+房)
 $6887万
 $48,500/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -39635,7 +39635,7 @@
           <t>B | 942呎 (3房)
 $4085万
 $43,364/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39643,7 +39643,7 @@
           <t>C | 589呎 (2房)
 $2025万
 $34,376/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -39651,7 +39651,7 @@
           <t>D | 481呎 (2房)
 $1591万
 $33,069/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -39659,7 +39659,7 @@
           <t>E | 524呎 (2房)
 $1686万
 $32,174/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -39667,7 +39667,7 @@
           <t>F | 464呎 (2房)
 $1598万
 $34,434/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -39682,7 +39682,7 @@
           <t>A | 1420呎 (4+房)
 $6929万
 $48,796/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -39690,7 +39690,7 @@
           <t>B | 941呎 (3房)
 $4168万
 $44,288/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -39698,7 +39698,7 @@
           <t>C | 589呎 (2房)
 $2019万
 $34,273/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -39706,7 +39706,7 @@
           <t>D | 481呎 (2房)
 $1510万
 $31,400/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -39714,7 +39714,7 @@
           <t>E | 524呎 (2房)
 $1678万
 $32,014/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -39722,7 +39722,7 @@
           <t>F | 464呎 (2房)
 $1640万
 $35,335/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -39737,7 +39737,7 @@
           <t>A | 1420呎 (4+房)
 $6958万
 $48,997/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>B | 941呎 (3房)
 $3930万
 $41,762/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>C | 589呎 (2房)
 $2013万
 $34,170/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -39761,7 +39761,7 @@
           <t>D | 481呎 (2房)
 $1544万
 $32,091/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -39769,7 +39769,7 @@
           <t>E | 524呎 (2房)
 $1735万
 $33,119/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -39777,7 +39777,7 @@
           <t>F | 464呎 (2房)
 $1566万
 $33,759/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -39792,7 +39792,7 @@
           <t>A | 1420呎 (4+房)
 $7009万
 $49,358/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -39800,7 +39800,7 @@
           <t>B | 942呎 (3房)
 $4085万
 $43,370/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39808,7 +39808,7 @@
           <t>C | 589呎 (2房)
 $1971万
 $33,459/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -39816,7 +39816,7 @@
           <t>D | 481呎 (2房)
 $1561万
 $32,449/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>E | 523呎 (2房)
 $1710万
 $32,689/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -39832,7 +39832,7 @@
           <t>F | 464呎 (2房)
 $1559万
 $33,591/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -39847,7 +39847,7 @@
           <t>A | 1420呎 (4+房)
 $6532万
 $46,002/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -39855,7 +39855,7 @@
           <t>B | 941呎 (3房)
 $3852万
 $40,938/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39863,7 +39863,7 @@
           <t>C | 589呎 (2房)
 $1905万
 $32,346/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -39871,7 +39871,7 @@
           <t>D | 481呎 (2房)
 $1334万
 $27,731/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -39879,7 +39879,7 @@
           <t>E | 524呎 (2房)
 $1620万
 $30,918/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -39887,7 +39887,7 @@
           <t>F | 464呎 (2房)
 $1299万
 $27,993/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -39902,7 +39902,7 @@
           <t>A | 1420呎 (4+房)
 $6816万
 $48,000/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -39910,7 +39910,7 @@
           <t>B | 942呎 (3房)
 $3905万
 $41,456/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -39918,7 +39918,7 @@
           <t>C | 589呎 (2房)
 $1900万
 $32,250/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -39926,7 +39926,7 @@
           <t>D | 481呎 (2房)
 $1524万
 $31,679/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -39934,7 +39934,7 @@
           <t>E | 523呎 (2房)
 $1646万
 $31,475/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -39942,7 +39942,7 @@
           <t>F | 464呎 (2房)
 $1528万
 $32,931/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -39957,7 +39957,7 @@
           <t>A | 1420呎 (4+房)
 $6404万
 $45,100/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -39965,7 +39965,7 @@
           <t>B | 942呎 (3房)
 $3695万
 $39,223/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39973,7 +39973,7 @@
           <t>C | 588呎 (2房)
 $1894万
 $32,211/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -39981,7 +39981,7 @@
           <t>D | 481呎 (2房)
 $1547万
 $32,159/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -39989,7 +39989,7 @@
           <t>E | 523呎 (2房)
 $1668万
 $31,888/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -39997,7 +39997,7 @@
           <t>F | 464呎 (2房)
 $1520万
 $32,766/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -40012,7 +40012,7 @@
           <t>A | 1420呎 (4+房)
 $6107万
 $43,010/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -40020,7 +40020,7 @@
           <t>B | 942呎 (3房)
 $3784万
 $40,167/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -40028,7 +40028,7 @@
           <t>C | 588呎 (2房)
 $1888万
 $32,114/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -40036,7 +40036,7 @@
           <t>D | 481呎 (2房)
 $1542万
 $32,063/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -40044,7 +40044,7 @@
           <t>E | 523呎 (2房)
 $1422万
 $27,196/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -40052,7 +40052,7 @@
           <t>F | 464呎 (2房)
 $1560万
 $33,621/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -40067,7 +40067,7 @@
           <t>A | 1420呎 (4+房)
 $5900万
 $41,549/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -40075,7 +40075,7 @@
           <t>B | 942呎 (3房)
 $3660万
 $38,854/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -40083,7 +40083,7 @@
           <t>C | 589呎 (2房)
 $1888万
 $32,060/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -40091,7 +40091,7 @@
           <t>D | 481呎 (2房)
 $1469万
 $30,536/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -40099,7 +40099,7 @@
           <t>E | 523呎 (2房)
 $1580万
 $30,218/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -40107,7 +40107,7 @@
           <t>F | 464呎 (2房)
 $1513万
 $32,602/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -40122,7 +40122,7 @@
           <t>A | 1420呎 (4+房)
 $6292万
 $44,308/呎
-(22年-06月)</t>
+(22年-06月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -40130,7 +40130,7 @@
           <t>B | 942呎 (3房)
 $3652万
 $38,770/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40138,7 +40138,7 @@
           <t>C | 588呎 (2房)
 $1971万
 $33,517/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -40146,7 +40146,7 @@
           <t>D | 481呎 (2房)
 $1460万
 $30,355/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -40154,7 +40154,7 @@
           <t>E | 523呎 (2房)
 $1565万
 $29,920/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -40162,7 +40162,7 @@
           <t>F | 464呎 (2房)
 $1535万
 $33,088/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -40177,7 +40177,7 @@
           <t>A | 1420呎 (4+房)
 $5623万
 $39,600/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -40185,7 +40185,7 @@
           <t>B | 942呎 (3房)
 $3627万
 $38,499/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40193,7 +40193,7 @@
           <t>C | 588呎 (2房)
 $1965万
 $33,416/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -40201,7 +40201,7 @@
           <t>D | 481呎 (2房)
 $1528万
 $31,777/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -40209,7 +40209,7 @@
           <t>E | 523呎 (2房)
 $1638万
 $31,321/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -40217,7 +40217,7 @@
           <t>F | 465呎 (2房)
 $1568万
 $33,719/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -40232,7 +40232,7 @@
           <t>A | 1420呎 (4+房)
 $6262万
 $44,101/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -40240,7 +40240,7 @@
           <t>B | 942呎 (3房)
 $3887万
 $41,258/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -40248,7 +40248,7 @@
           <t>C | 589呎 (2房)
 $1959万
 $33,261/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -40256,7 +40256,7 @@
           <t>D | 481呎 (2房)
 $1524万
 $31,684/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -40264,7 +40264,7 @@
           <t>E | 523呎 (2房)
 $1604万
 $30,670/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -40272,7 +40272,7 @@
           <t>F | 465呎 (2房)
 $1563万
 $33,618/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -40287,7 +40287,7 @@
           <t>A | 1420呎 (4+房)
 $6231万
 $43,881/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -40295,7 +40295,7 @@
           <t>B | 942呎 (3房)
 $3867万
 $41,053/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40303,7 +40303,7 @@
           <t>C | 588呎 (2房)
 $1860万
 $31,635/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -40311,7 +40311,7 @@
           <t>D | 481呎 (2房)
 $1447万
 $30,084/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -40319,7 +40319,7 @@
           <t>E | 523呎 (2房)
 $1628万
 $31,133/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -40327,7 +40327,7 @@
           <t>F | 464呎 (2房)
 $1559万
 $33,591/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -40342,7 +40342,7 @@
           <t>A | 1420呎 (4+房)
 $5905万
 $41,584/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -40350,7 +40350,7 @@
           <t>B | 942呎 (3房)
 $3555万
 $37,738/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40358,7 +40358,7 @@
           <t>C | 588呎 (2房)
 $1855万
 $31,541/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -40366,7 +40366,7 @@
           <t>D | 481呎 (2房)
 $1443万
 $29,993/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -40374,7 +40374,7 @@
           <t>E | 523呎 (2房)
 $1546万
 $29,562/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -40382,7 +40382,7 @@
           <t>F | 465呎 (2房)
 $1239万
 $26,653/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -40397,7 +40397,7 @@
           <t>A | 1420呎 (4+房)
 $5910万
 $41,618/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -40405,7 +40405,7 @@
           <t>B | 941呎 (3房)
 $3829万
 $40,689/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -40413,7 +40413,7 @@
           <t>C | 589呎 (2房)
 $1907万
 $32,375/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -40421,7 +40421,7 @@
           <t>D | 481呎 (2房)
 $1510万
 $31,398/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -40429,7 +40429,7 @@
           <t>E | 523呎 (2房)
 $1590万
 $30,396/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -40437,7 +40437,7 @@
           <t>F | 465呎 (2房)
 $1549万
 $33,315/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -40452,7 +40452,7 @@
           <t>A | 1420呎 (4+房)
 $5214万
 $36,721/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -40460,7 +40460,7 @@
           <t>B | 942呎 (3房)
 $3732万
 $39,616/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -40468,7 +40468,7 @@
           <t>C | 588呎 (2房)
 $1844万
 $31,354/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -40476,7 +40476,7 @@
           <t>D | 481呎 (2房)
 $1434万
 $29,813/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -40484,7 +40484,7 @@
           <t>E | 523呎 (2房)
 $1537万
 $29,386/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -40492,7 +40492,7 @@
           <t>F | 465呎 (2房)
 $1471万
 $31,635/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -40515,7 +40515,7 @@
           <t>B | 941呎 (3房)
 $3519万
 $37,396/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -40523,7 +40523,7 @@
           <t>C | 588呎 (2房)
 $1924万
 $32,724/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -40531,7 +40531,7 @@
           <t>D | 481呎 (2房)
 $1497万
 $31,119/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -40539,7 +40539,7 @@
           <t>E | 523呎 (2房)
 $1394万
 $26,657/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -40547,7 +40547,7 @@
           <t>F | 464呎 (2房)
 $1535万
 $33,091/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -40570,7 +40570,7 @@
           <t>B | 942呎 (3房)
 $3677万
 $39,029/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40578,7 +40578,7 @@
           <t>C | 588呎 (2房)
 $1918万
 $32,627/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -40586,7 +40586,7 @@
           <t>D | 481呎 (2房)
 $1492万
 $31,024/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -40594,7 +40594,7 @@
           <t>E | 523呎 (2房)
 $1599万
 $30,580/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -40602,7 +40602,7 @@
           <t>F | 465呎 (2房)
 $1531万
 $32,921/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -40617,7 +40617,7 @@
           <t>A | 1352呎 (4+房)
 $5556万
 $41,091/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -40625,7 +40625,7 @@
           <t>B | 882呎 (3房)
 $3902万
 $44,240/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40633,7 +40633,7 @@
           <t>C | 549呎 (2房)
 $1867万
 $34,001/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -40641,7 +40641,7 @@
           <t>D | 443呎 (2房)
 $1462万
 $33,000/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -40649,7 +40649,7 @@
           <t>E | 485呎 (2房)
 $1600万
 $33,000/呎
-(22年-02月)</t>
+(22年-02月-16日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -40657,7 +40657,7 @@
           <t>F | 425呎 (2房)
 $1424万
 $33,500/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -40841,7 +40841,7 @@
           <t>A | 955呎 (3房)
 $4102万
 $42,955/呎
-(22年-02月)</t>
+(22年-02月-16日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -40849,7 +40849,7 @@
           <t>B | 842呎 (3房)
 $3245万
 $38,536/呎
-(22年-03月)</t>
+(22年-03月-09日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -40857,7 +40857,7 @@
           <t>C | 850呎 (3房)
 $3476万
 $40,892/呎
-(23年-02月)</t>
+(23年-02月-26日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -40865,7 +40865,7 @@
           <t>D | 920呎 (3房)
 $3630万
 $39,454/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -40873,7 +40873,7 @@
           <t>E | 341呎 (1房)
 $1257万
 $36,874/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -40881,7 +40881,7 @@
           <t>F | 604呎 (2房)
 $1782万
 $29,499/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -40896,7 +40896,7 @@
           <t>A | 955呎 (3房)
 $3249万
 $34,024/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -40904,7 +40904,7 @@
           <t>B | 842呎 (3房)
 $3222万
 $38,268/呎
-(23年-03月)</t>
+(23年-03月-07日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -40912,7 +40912,7 @@
           <t>C | 850呎 (3房)
 $3452万
 $40,608/呎
-(23年-02月)</t>
+(23年-02月-26日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -40920,7 +40920,7 @@
           <t>D | 920呎 (3房)
 $3605万
 $39,180/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -40928,7 +40928,7 @@
           <t>E | 341呎 (1房)
 $1194万
 $35,012/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -40936,7 +40936,7 @@
           <t>F | 604呎 (2房)
 $1776万
 $29,409/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -40951,7 +40951,7 @@
           <t>A | 955呎 (3房)
 $3227万
 $33,788/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -40959,7 +40959,7 @@
           <t>B | 842呎 (3房)
 $3200万
 $38,002/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -40967,7 +40967,7 @@
           <t>C | 850呎 (3房)
 $2871万
 $33,772/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -40975,7 +40975,7 @@
           <t>D | 920呎 (3房)
 $3580万
 $38,908/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -40983,7 +40983,7 @@
           <t>E | 341呎 (1房)
 $1190万
 $34,904/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -40991,7 +40991,7 @@
           <t>F | 604呎 (2房)
 $1771万
 $29,323/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
     </row>
@@ -41006,7 +41006,7 @@
           <t>A | 955呎 (3房)
 $3634万
 $38,051/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -41014,7 +41014,7 @@
           <t>B | 842呎 (3房)
 $3289万
 $39,056/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -41022,7 +41022,7 @@
           <t>C | 850呎 (3房)
 $3233万
 $38,031/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -41030,7 +41030,7 @@
           <t>D | 921呎 (3房)
 $3487万
 $37,861/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -41038,7 +41038,7 @@
           <t>E | 341呎 (1房)
 $1246万
 $36,544/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -41046,7 +41046,7 @@
           <t>F | 604呎 (2房)
 $1766万
 $29,234/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -41061,7 +41061,7 @@
           <t>A | 955呎 (3房)
 $3609万
 $37,786/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -41069,7 +41069,7 @@
           <t>B | 842呎 (3房)
 $3110万
 $36,938/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -41077,7 +41077,7 @@
           <t>C | 850呎 (3房)
 $3210万
 $37,767/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -41085,7 +41085,7 @@
           <t>D | 921呎 (3房)
 $3298万
 $35,807/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -41093,7 +41093,7 @@
           <t>E | 341呎 (1房)
 $1183万
 $34,698/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -41101,7 +41101,7 @@
           <t>F | 604呎 (2房)
 $1760万
 $29,147/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -41116,7 +41116,7 @@
           <t>A | 955呎 (3房)
 $3584万
 $37,524/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -41124,7 +41124,7 @@
           <t>B | 842呎 (3房)
 $3185万
 $37,827/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -41132,7 +41132,7 @@
           <t>C | 850呎 (3房)
 $3188万
 $37,504/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -41140,7 +41140,7 @@
           <t>D | 921呎 (3房)
 $3439万
 $37,337/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -41148,7 +41148,7 @@
           <t>E | 341呎 (1房)
 $1180万
 $34,597/呎
-(21年-09月)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -41156,7 +41156,7 @@
           <t>F | 604呎 (2房)
 $1755万
 $29,060/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -41171,7 +41171,7 @@
           <t>A | 955呎 (3房)
 $3559万
 $37,263/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -41179,7 +41179,7 @@
           <t>B | 842呎 (3房)
 $3067万
 $36,426/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -41187,7 +41187,7 @@
           <t>C | 850呎 (3房)
 $3166万
 $37,242/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -41195,7 +41195,7 @@
           <t>D | 920呎 (3房)
 $3252万
 $35,349/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -41203,7 +41203,7 @@
           <t>E | 341呎 (1房)
 $1176万
 $34,494/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -41211,7 +41211,7 @@
           <t>F | 604呎 (2房)
 $1750万
 $28,973/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
           <t>A | 955呎 (3房)
 $3711万
 $38,854/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -41234,7 +41234,7 @@
           <t>B | 842呎 (3房)
 $3046万
 $36,172/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -41242,7 +41242,7 @@
           <t>C | 850呎 (3房)
 $3301万
 $38,834/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>D | 921呎 (3房)
 $3230万
 $35,066/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -41258,7 +41258,7 @@
           <t>E | 341呎 (1房)
 $1173万
 $34,391/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -41266,7 +41266,7 @@
           <t>F | 604呎 (2房)
 $2083万
 $34,490/呎
-(22年-02月)</t>
+(22年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -41281,7 +41281,7 @@
           <t>A | 955呎 (3房)
 $3711万
 $38,854/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41289,7 +41289,7 @@
           <t>B | 842呎 (3房)
 $3046万
 $36,172/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -41297,7 +41297,7 @@
           <t>C | 850呎 (3房)
 $3301万
 $38,834/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -41305,7 +41305,7 @@
           <t>D | 921呎 (3房)
 $3341万
 $36,275/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -41313,7 +41313,7 @@
           <t>E | 341呎 (1房)
 $949万
 $27,820/呎
-(24年-02月)</t>
+(24年-02月-06日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -41321,7 +41321,7 @@
           <t>F | 604呎 (2房)
 $1719万
 $28,458/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41336,7 @@
           <t>A | 955呎 (3房)
 $3485万
 $36,493/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -41344,7 +41344,7 @@
           <t>B | 842呎 (3房)
 $3004万
 $35,673/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -41352,7 +41352,7 @@
           <t>C | 850呎 (3房)
 $3100万
 $36,473/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -41360,7 +41360,7 @@
           <t>D | 921呎 (3房)
 $3295万
 $35,774/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -41368,7 +41368,7 @@
           <t>E | 341呎 (1房)
 $1126万
 $33,021/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -41376,7 +41376,7 @@
           <t>F | 604呎 (2房)
 $1745万
 $28,899/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -41391,7 +41391,7 @@
           <t>A | 955呎 (3房)
 $3356万
 $35,141/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -41399,7 +41399,7 @@
           <t>B | 842呎 (3房)
 $3132万
 $37,196/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -41407,7 +41407,7 @@
           <t>C | 850呎 (3房)
 $2950万
 $34,706/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -41415,7 +41415,7 @@
           <t>D | 921呎 (3房)
 $2993万
 $32,493/呎
-(24年-02月)</t>
+(24年-02月-19日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -41423,7 +41423,7 @@
           <t>E | 341呎 (1房)
 $1123万
 $32,922/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -41431,7 +41431,7 @@
           <t>F | 604呎 (2房)
 $1703万
 $28,203/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -41446,7 +41446,7 @@
           <t>A | 955呎 (3房)
 $3403万
 $35,632/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -41454,7 +41454,7 @@
           <t>B | 842呎 (3房)
 $3025万
 $35,921/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -41462,7 +41462,7 @@
           <t>C | 850呎 (3房)
 $3122万
 $36,728/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -41470,7 +41470,7 @@
           <t>D | 921呎 (3房)
 $3185万
 $34,584/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -41478,7 +41478,7 @@
           <t>E | 341呎 (1房)
 $1147万
 $33,644/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -41486,7 +41486,7 @@
           <t>F | 604呎 (2房)
 $1698万
 $28,120/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -41501,7 +41501,7 @@
           <t>A | 955呎 (3房)
 $3558万
 $37,253/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>B | 842呎 (3房)
 $2780万
 $33,017/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -41517,7 +41517,7 @@
           <t>C | 850呎 (3房)
 $3088万
 $36,328/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -41525,7 +41525,7 @@
           <t>D | 920呎 (3房)
 $2922万
 $31,761/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -41533,7 +41533,7 @@
           <t>E | 341呎 (1房)
 $1116万
 $32,727/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -41541,7 +41541,7 @@
           <t>F | 604呎 (2房)
 $2123万
 $35,149/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -41556,7 +41556,7 @@
           <t>A | 955呎 (3房)
 $3619万
 $37,897/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -41564,7 +41564,7 @@
           <t>B | 842呎 (3房)
 $3036万
 $36,051/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -41572,7 +41572,7 @@
           <t>C | 850呎 (3房)
 $3066万
 $36,075/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -41580,7 +41580,7 @@
           <t>D | 920呎 (3房)
 $2992万
 $32,517/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -41588,7 +41588,7 @@
           <t>E | 341呎 (1房)
 $1113万
 $32,629/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -41596,7 +41596,7 @@
           <t>F | 604呎 (2房)
 $2016万
 $33,374/呎
-(22年-07月)</t>
+(22年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -41611,7 +41611,7 @@
           <t>A | 955呎 (3房)
 $3423万
 $35,841/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -41619,7 +41619,7 @@
           <t>B | 842呎 (3房)
 $2843万
 $33,761/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -41627,7 +41627,7 @@
           <t>C | 850呎 (3房)
 $3045万
 $35,825/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -41635,7 +41635,7 @@
           <t>D | 921呎 (3房)
 $3045万
 $33,063/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -41643,7 +41643,7 @@
           <t>E | 341呎 (1房)
 $1144万
 $33,547/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -41651,7 +41651,7 @@
           <t>F | 604呎 (2房)
 $1683万
 $27,867/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -41666,7 +41666,7 @@
           <t>A | 955呎 (3房)
 $3399万
 $35,592/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -41674,7 +41674,7 @@
           <t>B | 842呎 (3房)
 $2823万
 $33,527/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -41682,7 +41682,7 @@
           <t>C | 850呎 (3房)
 $3175万
 $37,354/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -41690,7 +41690,7 @@
           <t>D | 920呎 (3房)
 $2950万
 $32,066/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -41698,7 +41698,7 @@
           <t>E | 341呎 (1房)
 $1106万
 $32,434/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -41706,7 +41706,7 @@
           <t>F | 604呎 (2房)
 $1678万
 $27,785/呎
-(24年-01月)</t>
+(24年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -41721,7 +41721,7 @@
           <t>A | 955呎 (3房)
 $3363万
 $35,218/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -41729,7 +41729,7 @@
           <t>B | 842呎 (3房)
 $2683万
 $31,860/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -41737,7 +41737,7 @@
           <t>C | 850呎 (3房)
 $2994万
 $35,229/呎
-(21年-09月)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -41745,7 +41745,7 @@
           <t>D | 921呎 (3房)
 $2935万
 $31,872/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -41753,7 +41753,7 @@
           <t>E | 341呎 (1房)
 $1103万
 $32,335/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -41761,7 +41761,7 @@
           <t>F | 604呎 (2房)
 $1998万
 $33,075/呎
-(21年-11月)</t>
+(21年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -41776,7 +41776,7 @@
           <t>A | 955呎 (3房)
 $3107万
 $32,534/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -41784,7 +41784,7 @@
           <t>B | 842呎 (3房)
 $2817万
 $33,453/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -41792,7 +41792,7 @@
           <t>C | 850呎 (3房)
 $2994万
 $35,229/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -41800,7 +41800,7 @@
           <t>D | 921呎 (3房)
 $3082万
 $33,466/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -41808,7 +41808,7 @@
           <t>E | 341呎 (1房)
 $1158万
 $33,952/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -41816,7 +41816,7 @@
           <t>F | 604呎 (2房)
 $1998万
 $33,075/呎
-(22年-01月)</t>
+(22年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -41831,7 +41831,7 @@
           <t>A | 955呎 (3房)
 $3330万
 $34,868/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -41839,7 +41839,7 @@
           <t>B | 842呎 (3房)
 $2566万
 $30,476/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -41847,7 +41847,7 @@
           <t>C | 850呎 (3房)
 $2965万
 $34,879/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -41855,7 +41855,7 @@
           <t>D | 920呎 (3房)
 $2906万
 $31,591/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -41863,7 +41863,7 @@
           <t>E | 341呎 (1房)
 $918万
 $26,920/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -41871,7 +41871,7 @@
           <t>F | 604呎 (2房)
 $1663万
 $27,537/呎
-(24年-02月)</t>
+(24年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -41886,7 +41886,7 @@
           <t>A | 955呎 (3房)
 $3156万
 $33,042/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -41894,7 +41894,7 @@
           <t>B | 842呎 (3房)
 $2632万
 $31,264/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -41902,7 +41902,7 @@
           <t>C | 850呎 (3房)
 $2809万
 $33,052/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -41910,7 +41910,7 @@
           <t>D | 921呎 (3房)
 $3037万
 $32,970/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -41918,7 +41918,7 @@
           <t>E | 341呎 (1房)
 $1147万
 $33,649/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -41926,7 +41926,7 @@
           <t>F | 604呎 (2房)
 $1658万
 $27,453/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -41941,7 +41941,7 @@
           <t>A | 955呎 (3房)
 $3297万
 $34,522/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -41949,7 +41949,7 @@
           <t>B | 842呎 (3房)
 $2619万
 $31,108/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -41957,7 +41957,7 @@
           <t>C | 850呎 (3房)
 $2795万
 $32,887/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -41965,7 +41965,7 @@
           <t>D | 921呎 (3房)
 $2878万
 $31,243/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -41973,7 +41973,7 @@
           <t>E | 341呎 (1房)
 $1090万
 $31,953/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -41981,7 +41981,7 @@
           <t>F | 604呎 (2房)
 $1653万
 $27,371/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -41996,7 +41996,7 @@
           <t>A | 955呎 (3房)
 $3037万
 $31,797/呎
-(24年-02月)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -42004,7 +42004,7 @@
           <t>B | 842呎 (3房)
 $2606万
 $30,953/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -42012,7 +42012,7 @@
           <t>C | 850呎 (3房)
 $2926万
 $34,428/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -42020,7 +42020,7 @@
           <t>D | 921呎 (3房)
 $2869万
 $31,150/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -42028,7 +42028,7 @@
           <t>E | 341呎 (1房)
 $1086万
 $31,859/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -42036,7 +42036,7 @@
           <t>F | 604呎 (2房)
 $2067万
 $34,215/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -42051,7 +42051,7 @@
           <t>A | 955呎 (3房)
 $3027万
 $31,701/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -42059,7 +42059,7 @@
           <t>B | 842呎 (3房)
 $2593万
 $30,798/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -42067,7 +42067,7 @@
           <t>C | 850呎 (3房)
 $2918万
 $34,325/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -42075,7 +42075,7 @@
           <t>D | 921呎 (3房)
 $2860万
 $31,057/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -42083,7 +42083,7 @@
           <t>E | 341呎 (1房)
 $1130万
 $33,150/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -42091,7 +42091,7 @@
           <t>F | 604呎 (2房)
 $1643万
 $27,208/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -42106,7 +42106,7 @@
           <t>A | 955呎 (3房)
 $3267万
 $34,212/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -42114,7 +42114,7 @@
           <t>B | 842呎 (3房)
 $2654万
 $31,516/呎
-(22年-06月)</t>
+(22年-06月-27日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -42122,7 +42122,7 @@
           <t>C | 850呎 (3房)
 $2909万
 $34,223/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -42130,7 +42130,7 @@
           <t>D | 921呎 (3房)
 $2852万
 $30,963/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -42138,7 +42138,7 @@
           <t>E | 341呎 (1房)
 $1127万
 $33,048/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -42146,7 +42146,7 @@
           <t>F | 604呎 (2房)
 $2054万
 $34,010/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -42161,7 +42161,7 @@
           <t>A | 955呎 (3房)
 $3112万
 $32,583/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -42169,7 +42169,7 @@
           <t>B | 842呎 (3房)
 $2709万
 $32,178/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -42177,7 +42177,7 @@
           <t>C | 850呎 (3房)
 $2770万
 $32,593/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -42185,7 +42185,7 @@
           <t>D | 921呎 (3房)
 $2923万
 $31,737/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -42193,7 +42193,7 @@
           <t>E | 341呎 (1房)
 $1134万
 $33,253/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -42201,7 +42201,7 @@
           <t>F | 604呎 (2房)
 $1634万
 $27,046/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -42216,7 +42216,7 @@
           <t>A | 955呎 (3房)
 $3248万
 $34,008/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42224,7 +42224,7 @@
           <t>B | 842呎 (3房)
 $2635万
 $31,291/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -42232,7 +42232,7 @@
           <t>C | 850呎 (3房)
 $2754万
 $32,398/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -42240,7 +42240,7 @@
           <t>D | 920呎 (3房)
 $2835万
 $30,810/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -42248,7 +42248,7 @@
           <t>E | 341呎 (1房)
 $1127万
 $33,056/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -42256,7 +42256,7 @@
           <t>F | 604呎 (2房)
 $1624万
 $26,885/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -42271,7 +42271,7 @@
           <t>A | 955呎 (3房)
 $3084万
 $32,291/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42279,7 +42279,7 @@
           <t>B | 842呎 (3房)
 $2606万
 $30,948/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -42287,7 +42287,7 @@
           <t>C | 850呎 (3房)
 $2746万
 $32,301/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -42295,7 +42295,7 @@
           <t>D | 921呎 (3房)
 $2826万
 $30,685/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -42303,7 +42303,7 @@
           <t>E | 341呎 (1房)
 $1070万
 $31,385/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -42311,7 +42311,7 @@
           <t>F | 604呎 (2房)
 $1619万
 $26,804/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -42326,7 +42326,7 @@
           <t>A | 901呎 (3房)
 $3244万
 $36,000/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -42334,7 +42334,7 @@
           <t>B | 797呎 (3房)
 $2778万
 $34,851/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -42342,7 +42342,7 @@
           <t>C | 799呎 (3房)
 $2916万
 $36,500/呎
-(22年-02月)</t>
+(22年-02月-08日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -42350,7 +42350,7 @@
           <t>D | 873呎 (3房)
 $3250万
 $37,232/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -42358,7 +42358,7 @@
           <t>E | 320呎 (1房)
 $841万
 $26,287/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -42366,7 +42366,7 @@
           <t>F | 566呎 (2房)
 $1840万
 $32,500/呎
-(22年-04月)</t>
+(22年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -42523,7 +42523,7 @@
           <t>B | 1431呎 (4+房)
 $6053万
 $42,300/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -42542,59 +42542,10 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -42602,12 +42553,61 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月-26日)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -42620,7 +42620,7 @@
           <t>A | 638呎 (2房)
 $2180万
 $34,170/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -42628,7 +42628,7 @@
           <t>B | 594呎 (2房)
 $1673万
 $28,166/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -42636,7 +42636,7 @@
           <t>C | 749呎 (3房)
 $2405万
 $32,115/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr"/>
@@ -42645,7 +42645,7 @@
           <t>E | 553呎 (2房)
 $2008万
 $36,302/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -42653,7 +42653,7 @@
           <t>F | 343呎 (1房)
 $1273万
 $37,124/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -42661,7 +42661,7 @@
           <t>G | 470呎 (2房)
 $1702万
 $36,208/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -42676,7 +42676,7 @@
           <t>A | 638呎 (2房)
 $2070万
 $32,446/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -42684,7 +42684,7 @@
           <t>B | 594呎 (2房)
 $1946万
 $32,761/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -42692,7 +42692,7 @@
           <t>C | 749呎 (3房)
 $2398万
 $32,021/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr"/>
@@ -42701,7 +42701,7 @@
           <t>E | 553呎 (2房)
 $2002万
 $36,195/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -42709,7 +42709,7 @@
           <t>F | 343呎 (1房)
 $1270万
 $37,014/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -42717,7 +42717,7 @@
           <t>G | 470呎 (2房)
 $1697万
 $36,099/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -42732,7 +42732,7 @@
           <t>A | 638呎 (2房)
 $2063万
 $32,335/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -42740,7 +42740,7 @@
           <t>B | 594呎 (2房)
 $1931万
 $32,504/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -42748,7 +42748,7 @@
           <t>C | 749呎 (3房)
 $2391万
 $31,925/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr"/>
@@ -42757,7 +42757,7 @@
           <t>E | 553呎 (2房)
 $1996万
 $36,088/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -42765,7 +42765,7 @@
           <t>F | 343呎 (1房)
 $1266万
 $36,904/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -42773,7 +42773,7 @@
           <t>G | 470呎 (2房)
 $1776万
 $37,791/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -42788,7 +42788,7 @@
           <t>A | 638呎 (2房)
 $2057万
 $32,237/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -42796,7 +42796,7 @@
           <t>B | 594呎 (2房)
 $1833万
 $30,865/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -42804,7 +42804,7 @@
           <t>C | 749呎 (3房)
 $2384万
 $31,828/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr"/>
@@ -42813,7 +42813,7 @@
           <t>E | 553呎 (2房)
 $1895万
 $34,265/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -42821,7 +42821,7 @@
           <t>F | 343呎 (1房)
 $1202万
 $35,039/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -42829,7 +42829,7 @@
           <t>G | 470呎 (2房)
 $1687万
 $35,884/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -42844,7 +42844,7 @@
           <t>A | 638呎 (2房)
 $1953万
 $30,609/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -42852,7 +42852,7 @@
           <t>B | 594呎 (2房)
 $1828万
 $30,770/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -42860,7 +42860,7 @@
           <t>C | 749呎 (3房)
 $2377万
 $31,733/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -42869,7 +42869,7 @@
           <t>E | 553呎 (2房)
 $1889万
 $34,164/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -42877,7 +42877,7 @@
           <t>F | 343呎 (1房)
 $1004万
 $29,259/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -42885,7 +42885,7 @@
           <t>G | 470呎 (2房)
 $1408万
 $29,963/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -42900,7 +42900,7 @@
           <t>A | 638呎 (2房)
 $1947万
 $30,519/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -42908,7 +42908,7 @@
           <t>B | 594呎 (2房)
 $1640万
 $27,611/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -42916,7 +42916,7 @@
           <t>C | 749呎 (3房)
 $2971万
 $39,666/呎
-(22年-01月)</t>
+(22年-01月-21日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -42925,7 +42925,7 @@
           <t>E | 553呎 (2房)
 $1884万
 $34,063/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -42933,7 +42933,7 @@
           <t>F | 343呎 (1房)
 $1254万
 $36,573/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -42941,7 +42941,7 @@
           <t>G | 470呎 (2房)
 $1404万
 $29,874/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -42956,7 +42956,7 @@
           <t>A | 638呎 (2房)
 $1941万
 $30,428/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -42964,7 +42964,7 @@
           <t>B | 594呎 (2房)
 $1908万
 $32,117/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -42972,7 +42972,7 @@
           <t>C | 749呎 (3房)
 $2363万
 $31,545/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -42981,7 +42981,7 @@
           <t>E | 553呎 (2房)
 $1878万
 $33,959/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -42989,7 +42989,7 @@
           <t>F | 343呎 (1房)
 $1251万
 $36,465/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -42997,7 +42997,7 @@
           <t>G | 470呎 (2房)
 $1400万
 $29,784/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -43012,7 +43012,7 @@
           <t>A | 638呎 (2房)
 $1913万
 $29,979/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -43020,7 +43020,7 @@
           <t>B | 594呎 (2房)
 $1861万
 $31,329/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -43028,7 +43028,7 @@
           <t>C | 749呎 (3房)
 $2339万
 $31,223/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -43037,7 +43037,7 @@
           <t>E | 553呎 (2房)
 $1850万
 $33,458/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -43045,7 +43045,7 @@
           <t>F | 343呎 (1房)
 $1174万
 $34,216/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -43053,7 +43053,7 @@
           <t>G | 470呎 (2房)
 $1647万
 $35,038/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -43068,7 +43068,7 @@
           <t>A | 638呎 (2房)
 $1996万
 $31,289/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -43076,7 +43076,7 @@
           <t>B | 594呎 (2房)
 $1762万
 $29,661/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -43084,7 +43084,7 @@
           <t>C | 749呎 (3房)
 $2673万
 $35,686/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -43093,7 +43093,7 @@
           <t>E | 553呎 (2房)
 $1839万
 $33,257/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -43101,7 +43101,7 @@
           <t>F | 343呎 (1房)
 $977万
 $28,484/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -43109,7 +43109,7 @@
           <t>G | 470呎 (2房)
 $1637万
 $34,829/呎
-(22年-05月)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -43124,7 +43124,7 @@
           <t>A | 638呎 (2房)
 $1990万
 $31,197/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -43132,7 +43132,7 @@
           <t>B | 594呎 (2房)
 $1844万
 $31,049/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -43140,7 +43140,7 @@
           <t>C | 749呎 (3房)
 $2665万
 $35,579/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -43149,7 +43149,7 @@
           <t>E | 553呎 (2房)
 $1925万
 $34,815/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -43157,7 +43157,7 @@
           <t>F | 343呎 (1房)
 $1221万
 $35,603/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -43165,7 +43165,7 @@
           <t>G | 470呎 (2房)
 $1632万
 $34,725/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -43180,7 +43180,7 @@
           <t>A | 638呎 (2房)
 $1965万
 $30,797/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43188,7 +43188,7 @@
           <t>B | 594呎 (2房)
 $1839万
 $30,957/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -43196,7 +43196,7 @@
           <t>C | 749呎 (3房)
 $2723万
 $36,359/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -43205,7 +43205,7 @@
           <t>E | 553呎 (2房)
 $1828万
 $33,060/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -43213,7 +43213,7 @@
           <t>F | 343呎 (1房)
 $1160万
 $33,808/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -43221,7 +43221,7 @@
           <t>G | 470呎 (2房)
 $1627万
 $34,620/呎
-(22年-01月)</t>
+(22年-01月-20日)</t>
         </is>
       </c>
     </row>
@@ -43236,7 +43236,7 @@
           <t>A | 638呎 (2房)
 $1866万
 $29,243/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43244,7 +43244,7 @@
           <t>B | 594呎 (2房)
 $1746万
 $29,395/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -43252,7 +43252,7 @@
           <t>C | 749呎 (3房)
 $2649万
 $35,367/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -43261,7 +43261,7 @@
           <t>E | 553呎 (2房)
 $1823万
 $32,961/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -43269,7 +43269,7 @@
           <t>F | 343呎 (1房)
 $1214万
 $35,393/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -43277,7 +43277,7 @@
           <t>G | 470呎 (2房)
 $1622万
 $34,517/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -43292,7 +43292,7 @@
           <t>A | 638呎 (2房)
 $1860万
 $29,155/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -43300,7 +43300,7 @@
           <t>B | 594呎 (2房)
 $1795万
 $30,224/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -43308,7 +43308,7 @@
           <t>C | 749呎 (3房)
 $2641万
 $35,262/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -43317,7 +43317,7 @@
           <t>E | 553呎 (2房)
 $1800万
 $32,547/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -43325,7 +43325,7 @@
           <t>F | 343呎 (1房)
 $1210万
 $35,290/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -43333,7 +43333,7 @@
           <t>G | 470呎 (2房)
 $1668万
 $35,489/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -43348,7 +43348,7 @@
           <t>A | 638呎 (2房)
 $1854万
 $29,067/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43356,7 +43356,7 @@
           <t>B | 594呎 (2房)
 $1736万
 $29,219/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -43364,7 +43364,7 @@
           <t>C | 749呎 (3房)
 $2765万
 $36,912/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -43373,7 +43373,7 @@
           <t>E | 553呎 (2房)
 $1615万
 $29,205/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -43381,7 +43381,7 @@
           <t>F | 343呎 (1房)
 $963万
 $28,064/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -43389,7 +43389,7 @@
           <t>G | 470呎 (2房)
 $1693万
 $36,027/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -43404,7 +43404,7 @@
           <t>A | 638呎 (2房)
 $1849万
 $28,979/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43412,7 +43412,7 @@
           <t>B | 594呎 (2房)
 $1817万
 $30,588/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -43420,7 +43420,7 @@
           <t>C | 749呎 (3房)
 $2625万
 $35,050/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr"/>
@@ -43429,7 +43429,7 @@
           <t>E | 553呎 (2房)
 $1879万
 $33,971/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -43437,7 +43437,7 @@
           <t>F | 343呎 (1房)
 $1146万
 $33,406/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -43445,7 +43445,7 @@
           <t>G | 470呎 (2房)
 $1688万
 $35,920/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -43460,7 +43460,7 @@
           <t>A | 638呎 (2房)
 $1936万
 $30,339/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43468,7 +43468,7 @@
           <t>B | 594呎 (2房)
 $1725万
 $29,045/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -43476,7 +43476,7 @@
           <t>C | 749呎 (3房)
 $2617万
 $34,946/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr"/>
@@ -43485,7 +43485,7 @@
           <t>E | 553呎 (2房)
 $1784万
 $32,255/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -43493,7 +43493,7 @@
           <t>F | 343呎 (1房)
 $1142万
 $33,308/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -43501,7 +43501,7 @@
           <t>G | 470呎 (2房)
 $1343万
 $28,565/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -43516,7 +43516,7 @@
           <t>A | 638呎 (2房)
 $1843万
 $28,894/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43524,7 +43524,7 @@
           <t>B | 594呎 (2房)
 $1779万
 $29,953/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -43532,7 +43532,7 @@
           <t>C | 749呎 (3房)
 $2748万
 $36,693/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -43541,7 +43541,7 @@
           <t>E | 553呎 (2房)
 $1784万
 $32,255/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -43549,7 +43549,7 @@
           <t>F | 343呎 (1房)
 $1142万
 $33,308/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -43557,7 +43557,7 @@
           <t>G | 470呎 (2房)
 $1653万
 $35,173/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -43572,7 +43572,7 @@
           <t>A | 638呎 (2房)
 $1832万
 $28,721/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -43580,7 +43580,7 @@
           <t>B | 594呎 (2房)
 $1715万
 $28,873/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -43588,7 +43588,7 @@
           <t>C | 749呎 (3房)
 $2602万
 $34,736/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr"/>
@@ -43597,7 +43597,7 @@
           <t>E | 553呎 (2房)
 $1773万
 $32,062/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -43605,7 +43605,7 @@
           <t>F | 343呎 (1房)
 $1136万
 $33,108/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -43613,7 +43613,7 @@
           <t>G | 470呎 (2房)
 $1593万
 $33,903/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -43628,7 +43628,7 @@
           <t>A | 638呎 (2房)
 $1873万
 $29,350/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -43636,7 +43636,7 @@
           <t>B | 594呎 (2房)
 $1753万
 $29,506/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -43644,7 +43644,7 @@
           <t>C | 749呎 (3房)
 $2724万
 $36,364/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr"/>
@@ -43653,7 +43653,7 @@
           <t>E | 553呎 (2房)
 $1591万
 $28,770/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -43661,7 +43661,7 @@
           <t>F | 343呎 (1房)
 $1132万
 $33,008/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -43669,7 +43669,7 @@
           <t>G | 470呎 (2房)
 $1330万
 $28,308/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -43684,7 +43684,7 @@
           <t>A | 638呎 (2房)
 $1867万
 $29,263/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -43692,7 +43692,7 @@
           <t>B | 594呎 (2房)
 $1790万
 $30,135/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -43700,7 +43700,7 @@
           <t>C | 749呎 (3房)
 $2586万
 $34,529/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr"/>
@@ -43709,7 +43709,7 @@
           <t>E | 553呎 (2房)
 $1851万
 $33,463/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -43717,7 +43717,7 @@
           <t>F | 343呎 (1房)
 $1157万
 $33,732/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -43725,7 +43725,7 @@
           <t>G | 470呎 (2房)
 $1584万
 $33,699/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -43740,7 +43740,7 @@
           <t>A | 638呎 (2房)
 $1861万
 $29,176/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -43748,7 +43748,7 @@
           <t>B | 594呎 (2房)
 $1700万
 $28,614/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -43756,7 +43756,7 @@
           <t>C | 749呎 (3房)
 $2707万
 $36,148/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr"/>
@@ -43765,7 +43765,7 @@
           <t>E | 553呎 (2房)
 $1757万
 $31,776/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -43773,7 +43773,7 @@
           <t>F | 343呎 (1房)
 $1125万
 $32,809/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -43781,7 +43781,7 @@
           <t>G | 470呎 (2房)
 $1579万
 $33,598/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
           <t>A | 638呎 (2房)
 $1901万
 $29,799/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -43804,7 +43804,7 @@
           <t>B | 594呎 (2房)
 $1525万
 $25,674/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -43812,7 +43812,7 @@
           <t>C | 749呎 (3房)
 $2699万
 $36,040/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr"/>
@@ -43821,7 +43821,7 @@
           <t>E | 553呎 (2房)
 $1752万
 $31,680/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -43829,7 +43829,7 @@
           <t>F | 343呎 (1房)
 $1122万
 $32,714/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -43837,7 +43837,7 @@
           <t>G | 470呎 (2房)
 $1574万
 $33,500/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -43852,7 +43852,7 @@
           <t>A | 638呎 (2房)
 $1895万
 $29,709/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -43860,7 +43860,7 @@
           <t>B | 594呎 (2房)
 $1690万
 $28,443/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -43868,7 +43868,7 @@
           <t>C | 749呎 (3房)
 $2691万
 $35,932/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr"/>
@@ -43877,7 +43877,7 @@
           <t>E | 553呎 (2房)
 $1834万
 $33,164/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -43885,7 +43885,7 @@
           <t>F | 343呎 (1房)
 $1175万
 $34,249/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -43893,7 +43893,7 @@
           <t>G | 470呎 (2房)
 $1315万
 $27,972/呎
-(23年-12月)</t>
+(23年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -43908,7 +43908,7 @@
           <t>A | 638呎 (2房)
 $1895万
 $29,709/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -43916,7 +43916,7 @@
           <t>B | 544呎 (2房)
 $1578万
 $29,012/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -43924,7 +43924,7 @@
           <t>C | 469呎 (2房)
 $1491万
 $31,792/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -43932,7 +43932,7 @@
           <t>D | 335呎 (1房)
 $1158万
 $34,553/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -43940,7 +43940,7 @@
           <t>E | 553呎 (2房)
 $1572万
 $28,426/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -43948,7 +43948,7 @@
           <t>F | 343呎 (1房)
 $934万
 $27,238/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -43956,7 +43956,7 @@
           <t>G | 470呎 (2房)
 $1311万
 $27,888/呎
-(24年-02月)</t>
+(24年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -43971,7 +43971,7 @@
           <t>A | 638呎 (2房)
 $1794万
 $28,125/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -43979,7 +43979,7 @@
           <t>B | 544呎 (2房)
 $1647万
 $30,280/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -43987,7 +43987,7 @@
           <t>C | 470呎 (2房)
 $1556万
 $33,110/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -43995,7 +43995,7 @@
           <t>D | 335呎 (1房)
 $913万
 $27,262/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -44003,7 +44003,7 @@
           <t>E | 553呎 (2房)
 $1766万
 $31,931/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -44011,7 +44011,7 @@
           <t>F | 343呎 (1房)
 $1103万
 $32,170/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -44019,7 +44019,7 @@
           <t>G | 470呎 (2房)
 $1303万
 $27,722/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -44034,7 +44034,7 @@
           <t>A | 638呎 (2房)
 $1610万
 $25,236/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -44042,7 +44042,7 @@
           <t>B | 545呎 (2房)
 $1642万
 $30,134/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -44050,7 +44050,7 @@
           <t>C | 469呎 (2房)
 $1478万
 $31,509/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -44058,7 +44058,7 @@
           <t>D | 335呎 (1房)
 $1110万
 $33,143/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -44066,7 +44066,7 @@
           <t>E | 553呎 (2房)
 $1531万
 $27,680/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -44074,7 +44074,7 @@
           <t>F | 343呎 (1房)
 $1144万
 $33,348/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -44082,7 +44082,7 @@
           <t>G | 470呎 (2房)
 $1299万
 $27,638/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -44097,7 +44097,7 @@
           <t>A | 598呎 (2房)
 $2003万
 $33,500/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -44105,7 +44105,7 @@
           <t>B | 506呎 (2房)
 $1594万
 $31,500/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -44113,7 +44113,7 @@
           <t>C | 436呎 (2房)
 $1405万
 $32,226/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr"/>
@@ -44124,7 +44124,7 @@
           <t>G | 442呎 (2房)
 $1222万
 $27,637/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
     </row>
